--- a/src/grafs_e/data/scenario_region/Linear/Loire aval.xlsx
+++ b/src/grafs_e/data/scenario_region/Linear/Loire aval.xlsx
@@ -443,6 +443,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
@@ -464,6 +465,7 @@
         </is>
       </c>
     </row>
+    <row r="6"/>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
@@ -492,6 +494,7 @@
         </is>
       </c>
     </row>
+    <row r="11"/>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
@@ -499,6 +502,7 @@
         </is>
       </c>
     </row>
+    <row r="13"/>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
@@ -506,6 +510,7 @@
         </is>
       </c>
     </row>
+    <row r="15"/>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
@@ -550,7 +555,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E14"/>
+  <dimension ref="A1:E13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -781,23 +786,6 @@
       <c r="E13" t="inlineStr">
         <is>
           <t>No business as usual: computed with optimization model to fertilize all crops</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>Methanisation</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>GWh</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>2021 data. Used as a goal but may be adjusted according to territory situation</t>
         </is>
       </c>
     </row>
@@ -1647,7 +1635,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E57"/>
+  <dimension ref="A1:E55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1684,7 +1672,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -1740,37 +1728,41 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Weight export</t>
-        </is>
-      </c>
-      <c r="C6" t="n">
-        <v>2</v>
+          <t>N recycling rate of human excretion in urban area</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Weight for the optimization model</t>
+          <t>Taken as the last historical value</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Weight energy</t>
-        </is>
-      </c>
-      <c r="C7" t="n">
-        <v>2</v>
+          <t>N recycling rate of human excretion in rural area</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Weight for the optimization model</t>
+          <t>Taken as the last historical value</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>N recycling rate of human excretion in urban area</t>
+          <t>NH3 volatilization coefficient for synthetic nitrogen</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1787,7 +1779,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>N recycling rate of human excretion in rural area</t>
+          <t>Indirect N2O volatilization coefficient for synthetic nitrogen</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1804,41 +1796,41 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>NH3 volatilization coefficient for synthetic nitrogen</t>
+          <t>kgN excreted by bovines LU</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>%</t>
+          <t>kgN</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Taken as the last historical value</t>
+          <t>Historical trend</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Indirect N2O volatilization coefficient for synthetic nitrogen</t>
+          <t>kgN excreted by equines LU</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>%</t>
+          <t>kgN</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Taken as the last historical value</t>
+          <t>Historical trend</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>kgN excreted by bovines LU</t>
+          <t>kgN excreted by caprines LU</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1855,7 +1847,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>kgN excreted by equines LU</t>
+          <t>kgN excreted by ovines LU</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1872,7 +1864,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>kgN excreted by caprines LU</t>
+          <t>kgN excreted by porcines LU</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1889,7 +1881,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>kgN excreted by ovines LU</t>
+          <t>kgN excreted by poultry LU</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1906,41 +1898,41 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>kgN excreted by porcines LU</t>
+          <t>Bovines % excretion on grassland</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>kgN</t>
+          <t>%</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Historical trend</t>
+          <t>Taken as the last historical value</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>kgN excreted by poultry LU</t>
+          <t>Bovines % excretion in the barn as litter manure</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>kgN</t>
+          <t>%</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Historical trend</t>
+          <t>Taken as the last historical value</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Bovines % excretion on grassland</t>
+          <t>Bovines % excretion in the barn as other manure</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1957,7 +1949,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Bovines % excretion in the barn as litter manure</t>
+          <t>Bovines % excretion in the barn as slurry</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1974,7 +1966,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Bovines % excretion in the barn as other manure</t>
+          <t>Ovines % excretion on grassland</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1991,7 +1983,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Bovines % excretion in the barn as slurry</t>
+          <t>Ovines % excretion in the barn as litter manure</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2008,7 +2000,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Ovines % excretion on grassland</t>
+          <t>Ovines % excretion in the barn as other manure</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2025,7 +2017,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Ovines % excretion in the barn as litter manure</t>
+          <t>Ovines % excretion in the barn as slurry</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2042,7 +2034,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Ovines % excretion in the barn as other manure</t>
+          <t>Equines % excretion on grassland</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2059,7 +2051,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Ovines % excretion in the barn as slurry</t>
+          <t>Equines % excretion in the barn as litter manure</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2076,7 +2068,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Equines % excretion on grassland</t>
+          <t>Equines % excretion in the barn as other manure</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2093,7 +2085,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Equines % excretion in the barn as litter manure</t>
+          <t>Equines % excretion in the barn as slurry</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2110,7 +2102,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Equines % excretion in the barn as other manure</t>
+          <t>Caprines % excretion on grassland</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2127,7 +2119,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Equines % excretion in the barn as slurry</t>
+          <t>Caprines % excretion in the barn as litter manure</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2144,7 +2136,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Caprines % excretion on grassland</t>
+          <t>Caprines % excretion in the barn as other manure</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2161,7 +2153,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Caprines % excretion in the barn as litter manure</t>
+          <t>Caprines % excretion in the barn as slurry</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2178,7 +2170,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Caprines % excretion in the barn as other manure</t>
+          <t>Porcines % excretion on grassland</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2195,7 +2187,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Caprines % excretion in the barn as slurry</t>
+          <t>Porcines % excretion in the barn as litter manure</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2212,7 +2204,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Porcines % excretion on grassland</t>
+          <t>Porcines % excretion in the barn as other manure</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2229,7 +2221,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Porcines % excretion in the barn as litter manure</t>
+          <t>Porcines % excretion in the barn as slurry</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2246,7 +2238,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Porcines % excretion in the barn as other manure</t>
+          <t>Poultry % excretion on grassland</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2263,7 +2255,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Porcines % excretion in the barn as slurry</t>
+          <t>Poultry % excretion in the barn as litter manure</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2280,7 +2272,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Poultry % excretion on grassland</t>
+          <t>Poultry % excretion in the barn as other manure</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2297,7 +2289,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Poultry % excretion in the barn as litter manure</t>
+          <t>Poultry % excretion in the barn as slurry</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2314,12 +2306,12 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Poultry % excretion in the barn as other manure</t>
+          <t>Bovines LU</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>%</t>
+          <t>prop</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -2331,12 +2323,12 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Poultry % excretion in the barn as slurry</t>
+          <t>Ovines LU</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>%</t>
+          <t>prop</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -2348,7 +2340,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Bovines LU</t>
+          <t>Caprines LU</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -2365,7 +2357,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Ovines LU</t>
+          <t>Equines LU</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -2382,7 +2374,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Caprines LU</t>
+          <t>Porcines LU</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -2399,7 +2391,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Equines LU</t>
+          <t>Poultry LU</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -2416,41 +2408,41 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Porcines LU</t>
+          <t>Bovines productivity</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>prop</t>
+          <t>kgcarcass/LU</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Taken as the last historical value</t>
+          <t>These groups are taken as a whole even if only a part is producing meat, milk or eggs. Taken as the last historical value</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Poultry LU</t>
+          <t>Ovines productivity</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>prop</t>
+          <t>kgcarcass/LU</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Taken as the last historical value</t>
+          <t>These groups are taken as a whole even if only a part is producing meat, milk or eggs. Taken as the last historical value</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Bovines productivity</t>
+          <t>Caprines productivity</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2467,7 +2459,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Ovines productivity</t>
+          <t>Equines productivity</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2484,7 +2476,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Caprines productivity</t>
+          <t>Porcines productivity</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -2501,7 +2493,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Equines productivity</t>
+          <t>Poultry productivity</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -2518,12 +2510,12 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Porcines productivity</t>
+          <t>Bovines dairy productivity</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>kgcarcass/LU</t>
+          <t>kg/LU</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -2535,12 +2527,12 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Poultry productivity</t>
+          <t>Ovines dairy productivity</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>kgcarcass/LU</t>
+          <t>kg/LU</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -2552,7 +2544,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Bovines dairy productivity</t>
+          <t>Caprines dairy productivity</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -2569,7 +2561,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Ovines dairy productivity</t>
+          <t>Poultry dairy productivity</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -2578,40 +2570,6 @@
         </is>
       </c>
       <c r="E55" t="inlineStr">
-        <is>
-          <t>These groups are taken as a whole even if only a part is producing meat, milk or eggs. Taken as the last historical value</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" t="inlineStr">
-        <is>
-          <t>Caprines dairy productivity</t>
-        </is>
-      </c>
-      <c r="B56" t="inlineStr">
-        <is>
-          <t>kg/LU</t>
-        </is>
-      </c>
-      <c r="E56" t="inlineStr">
-        <is>
-          <t>These groups are taken as a whole even if only a part is producing meat, milk or eggs. Taken as the last historical value</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" t="inlineStr">
-        <is>
-          <t>Poultry dairy productivity</t>
-        </is>
-      </c>
-      <c r="B57" t="inlineStr">
-        <is>
-          <t>kg/LU</t>
-        </is>
-      </c>
-      <c r="E57" t="inlineStr">
         <is>
           <t>These groups are taken as a whole even if only a part is producing meat, milk or eggs. Taken as the last historical value</t>
         </is>

--- a/src/grafs_e/data/scenario_region/Linear/Loire aval.xlsx
+++ b/src/grafs_e/data/scenario_region/Linear/Loire aval.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="doc" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="main" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="area" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="technical" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="doc" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="main" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="area" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="technical" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -439,21 +439,17 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t> </t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr"/>
-      <c r="B2" t="inlineStr"/>
-    </row>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+    </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
           <t>create your scenario with basic data in main scenario tab. Add your scenario values in scenario column</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -461,7 +457,6 @@
           <t>if no value is given, the business as usual value will be used</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -469,19 +464,14 @@
           <t>if the territory requested is not found in the data, the business as usual column will be blank and you have to define all variables.</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr"/>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr"/>
-      <c r="B6" t="inlineStr"/>
-    </row>
+    </row>
+    <row r="6"/>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
           <t>Surface change tab is used to give general indication of crop rotation. This will give specific surface constraint for the model.</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -489,7 +479,6 @@
           <t>In culture field add the name of the culture and the scenario surface</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -497,7 +486,6 @@
           <t>You can enforce the given values by adding TRUE in the enforce column. Caution, if the sum of the enforced area is beyond total surface area, you will get an error.</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -505,43 +493,30 @@
           <t>For all culture not mentionned in the surface change tab, their surface will be deduced from previous historical data and scenario input</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr"/>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr"/>
-      <c r="B11" t="inlineStr"/>
-    </row>
+    </row>
+    <row r="11"/>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
           <t>Use technical scenario to change secondary parameters of the model</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr"/>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr"/>
-      <c r="B13" t="inlineStr"/>
-    </row>
+    </row>
+    <row r="13"/>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
           <t>BAU compute Business as usual scenario</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr"/>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr"/>
-      <c r="B15" t="inlineStr"/>
-    </row>
+    </row>
+    <row r="15"/>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
           <t>Scenario name</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -549,7 +524,6 @@
           <t>Region name</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -557,7 +531,6 @@
           <t>Year</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -582,31 +555,31 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E12"/>
+  <dimension ref="A1:E13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Variable</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>Unit</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>Business as usual</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Scenario</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>comment</t>
         </is>
@@ -623,8 +596,6 @@
           <t>M inhabitant</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr"/>
-      <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
           <t>INSEE data</t>
@@ -642,8 +613,6 @@
           <t>%</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr"/>
-      <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
           <t>Logistic</t>
@@ -661,8 +630,6 @@
           <t>kgN/cap/yr</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr"/>
-      <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
           <t>Taken as the last historical value</t>
@@ -680,8 +647,6 @@
           <t>kgN/cap/yr</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr"/>
-      <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
           <t>Taken as the last historical value</t>
@@ -699,8 +664,6 @@
           <t>kgN/cap/yr</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr"/>
-      <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
           <t>Taken as the last historical value</t>
@@ -718,8 +681,6 @@
           <t>ha</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr"/>
-      <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
           <t>Historical trend</t>
@@ -737,8 +698,6 @@
           <t>ha</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr"/>
-      <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
           <t>Historical trend</t>
@@ -748,7 +707,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Net import of vegetal pdcts</t>
+          <t>Import of vegetal pdcts</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -756,66 +715,75 @@
           <t>ktN</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr"/>
-      <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Historical trend. Used as a goal but may be adjusted according to territory situation</t>
+          <t>2006 data. Used as a goal but may be adjusted according to territory situation</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Total LU</t>
+          <t>Export of vegetal pdcts</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>LU</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr"/>
-      <c r="D10" t="inlineStr"/>
+          <t>ktN</t>
+        </is>
+      </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Historical trend, see prop for each livestock in technical sheet</t>
+          <t>2006 data. Used as a goal but may be adjusted according to territory situation</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Synth N fertilizer application to cropland</t>
+          <t>Total LU</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>kgN/ha/yr</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr"/>
-      <c r="D11" t="inlineStr"/>
+          <t>LU</t>
+        </is>
+      </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>No business as usual: computed with optimization model to fertilize all crops</t>
+          <t>Historical trend, see prop for each livestock in technical sheet</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
+          <t>Synth N fertilizer application to cropland</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>kgN/ha/yr</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>No business as usual: computed with optimization model to fertilize all crops</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
           <t>Synth N fertilizer application to grassland</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="B13" t="inlineStr">
         <is>
           <t>kgN/ha/yr</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr"/>
-      <c r="D12" t="inlineStr"/>
-      <c r="E12" t="inlineStr">
+      <c r="E13" t="inlineStr">
         <is>
           <t>No business as usual: computed with optimization model to fertilize all crops</t>
         </is>
@@ -1643,7 +1611,6 @@
           <t xml:space="preserve">Natural meadow </t>
         </is>
       </c>
-      <c r="B37" t="inlineStr"/>
       <c r="C37" t="b">
         <v>0</v>
       </c>
@@ -1668,31 +1635,31 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E54"/>
+  <dimension ref="A1:E55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Variable</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>unit</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>Business as usual</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Scenario</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>Comment</t>
         </is>
@@ -1704,11 +1671,9 @@
           <t>Weight diet</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr"/>
       <c r="C2" t="n">
         <v>1</v>
       </c>
-      <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
           <t>Weight for the optimization model</t>
@@ -1721,11 +1686,9 @@
           <t>Weight synthetic fertilizer use</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr"/>
       <c r="C3" t="n">
         <v>5</v>
       </c>
-      <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
           <t>Weight for the optimization model</t>
@@ -1735,14 +1698,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Weight import/export balance</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr"/>
+          <t>Weight import</t>
+        </is>
+      </c>
       <c r="C4" t="n">
         <v>2</v>
       </c>
-      <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
           <t>Weight for the optimization model</t>
@@ -1752,26 +1713,22 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>N recycling rate of human excretion in urban area</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>%</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr"/>
-      <c r="D5" t="inlineStr"/>
+          <t>Weight export</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>2</v>
+      </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Taken as the last historical value</t>
+          <t>Weight for the optimization model</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>N recycling rate of human excretion in rural area</t>
+          <t>N recycling rate of human excretion in urban area</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1779,8 +1736,6 @@
           <t>%</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr"/>
-      <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
           <t>Taken as the last historical value</t>
@@ -1790,7 +1745,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>NH3 volatilization coefficient for synthetic nitrogen</t>
+          <t>N recycling rate of human excretion in rural area</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1798,8 +1753,6 @@
           <t>%</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr"/>
-      <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
           <t>Taken as the last historical value</t>
@@ -1809,7 +1762,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Indirect N2O volatilization coefficient for synthetic nitrogen</t>
+          <t>NH3 volatilization coefficient for synthetic nitrogen</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1817,8 +1770,6 @@
           <t>%</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr"/>
-      <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
           <t>Taken as the last historical value</t>
@@ -1828,26 +1779,24 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>kgN excreted by bovines LU</t>
+          <t>Indirect N2O volatilization coefficient for synthetic nitrogen</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>kgN</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr"/>
-      <c r="D9" t="inlineStr"/>
+          <t>%</t>
+        </is>
+      </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Historical trend</t>
+          <t>Taken as the last historical value</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>kgN excreted by equines LU</t>
+          <t>kgN excreted by bovines LU</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1855,8 +1804,6 @@
           <t>kgN</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr"/>
-      <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
           <t>Historical trend</t>
@@ -1866,7 +1813,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>kgN excreted by caprines LU</t>
+          <t>kgN excreted by equines LU</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1874,8 +1821,6 @@
           <t>kgN</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr"/>
-      <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
           <t>Historical trend</t>
@@ -1885,7 +1830,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>kgN excreted by ovines LU</t>
+          <t>kgN excreted by caprines LU</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1893,8 +1838,6 @@
           <t>kgN</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr"/>
-      <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
           <t>Historical trend</t>
@@ -1904,7 +1847,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>kgN excreted by porcines LU</t>
+          <t>kgN excreted by ovines LU</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1912,8 +1855,6 @@
           <t>kgN</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr"/>
-      <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
         <is>
           <t>Historical trend</t>
@@ -1923,7 +1864,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>kgN excreted by poultry LU</t>
+          <t>kgN excreted by porcines LU</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1931,8 +1872,6 @@
           <t>kgN</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr"/>
-      <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr">
         <is>
           <t>Historical trend</t>
@@ -1942,26 +1881,24 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Bovines % excretion on grassland</t>
+          <t>kgN excreted by poultry LU</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>%</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr"/>
-      <c r="D15" t="inlineStr"/>
+          <t>kgN</t>
+        </is>
+      </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Taken as the last historical value</t>
+          <t>Historical trend</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Bovines % excretion in the barn as litter manure</t>
+          <t>Bovines % excretion on grassland</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1969,8 +1906,6 @@
           <t>%</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr"/>
-      <c r="D16" t="inlineStr"/>
       <c r="E16" t="inlineStr">
         <is>
           <t>Taken as the last historical value</t>
@@ -1980,7 +1915,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Bovines % excretion in the barn as other manure</t>
+          <t>Bovines % excretion in the barn as litter manure</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1988,8 +1923,6 @@
           <t>%</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr"/>
-      <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr">
         <is>
           <t>Taken as the last historical value</t>
@@ -1999,7 +1932,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Bovines % excretion in the barn as slurry</t>
+          <t>Bovines % excretion in the barn as other manure</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2007,8 +1940,6 @@
           <t>%</t>
         </is>
       </c>
-      <c r="C18" t="inlineStr"/>
-      <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr">
         <is>
           <t>Taken as the last historical value</t>
@@ -2018,7 +1949,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Ovines % excretion on grassland</t>
+          <t>Bovines % excretion in the barn as slurry</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2026,8 +1957,6 @@
           <t>%</t>
         </is>
       </c>
-      <c r="C19" t="inlineStr"/>
-      <c r="D19" t="inlineStr"/>
       <c r="E19" t="inlineStr">
         <is>
           <t>Taken as the last historical value</t>
@@ -2037,7 +1966,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Ovines % excretion in the barn as litter manure</t>
+          <t>Ovines % excretion on grassland</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2045,8 +1974,6 @@
           <t>%</t>
         </is>
       </c>
-      <c r="C20" t="inlineStr"/>
-      <c r="D20" t="inlineStr"/>
       <c r="E20" t="inlineStr">
         <is>
           <t>Taken as the last historical value</t>
@@ -2056,7 +1983,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Ovines % excretion in the barn as other manure</t>
+          <t>Ovines % excretion in the barn as litter manure</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2064,8 +1991,6 @@
           <t>%</t>
         </is>
       </c>
-      <c r="C21" t="inlineStr"/>
-      <c r="D21" t="inlineStr"/>
       <c r="E21" t="inlineStr">
         <is>
           <t>Taken as the last historical value</t>
@@ -2075,7 +2000,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Ovines % excretion in the barn as slurry</t>
+          <t>Ovines % excretion in the barn as other manure</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2083,8 +2008,6 @@
           <t>%</t>
         </is>
       </c>
-      <c r="C22" t="inlineStr"/>
-      <c r="D22" t="inlineStr"/>
       <c r="E22" t="inlineStr">
         <is>
           <t>Taken as the last historical value</t>
@@ -2094,7 +2017,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Equines % excretion on grassland</t>
+          <t>Ovines % excretion in the barn as slurry</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2102,8 +2025,6 @@
           <t>%</t>
         </is>
       </c>
-      <c r="C23" t="inlineStr"/>
-      <c r="D23" t="inlineStr"/>
       <c r="E23" t="inlineStr">
         <is>
           <t>Taken as the last historical value</t>
@@ -2113,7 +2034,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Equines % excretion in the barn as litter manure</t>
+          <t>Equines % excretion on grassland</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2121,8 +2042,6 @@
           <t>%</t>
         </is>
       </c>
-      <c r="C24" t="inlineStr"/>
-      <c r="D24" t="inlineStr"/>
       <c r="E24" t="inlineStr">
         <is>
           <t>Taken as the last historical value</t>
@@ -2132,7 +2051,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Equines % excretion in the barn as other manure</t>
+          <t>Equines % excretion in the barn as litter manure</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2140,8 +2059,6 @@
           <t>%</t>
         </is>
       </c>
-      <c r="C25" t="inlineStr"/>
-      <c r="D25" t="inlineStr"/>
       <c r="E25" t="inlineStr">
         <is>
           <t>Taken as the last historical value</t>
@@ -2151,7 +2068,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Equines % excretion in the barn as slurry</t>
+          <t>Equines % excretion in the barn as other manure</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2159,8 +2076,6 @@
           <t>%</t>
         </is>
       </c>
-      <c r="C26" t="inlineStr"/>
-      <c r="D26" t="inlineStr"/>
       <c r="E26" t="inlineStr">
         <is>
           <t>Taken as the last historical value</t>
@@ -2170,7 +2085,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Caprines % excretion on grassland</t>
+          <t>Equines % excretion in the barn as slurry</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2178,8 +2093,6 @@
           <t>%</t>
         </is>
       </c>
-      <c r="C27" t="inlineStr"/>
-      <c r="D27" t="inlineStr"/>
       <c r="E27" t="inlineStr">
         <is>
           <t>Taken as the last historical value</t>
@@ -2189,7 +2102,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Caprines % excretion in the barn as litter manure</t>
+          <t>Caprines % excretion on grassland</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2197,8 +2110,6 @@
           <t>%</t>
         </is>
       </c>
-      <c r="C28" t="inlineStr"/>
-      <c r="D28" t="inlineStr"/>
       <c r="E28" t="inlineStr">
         <is>
           <t>Taken as the last historical value</t>
@@ -2208,7 +2119,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Caprines % excretion in the barn as other manure</t>
+          <t>Caprines % excretion in the barn as litter manure</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2216,8 +2127,6 @@
           <t>%</t>
         </is>
       </c>
-      <c r="C29" t="inlineStr"/>
-      <c r="D29" t="inlineStr"/>
       <c r="E29" t="inlineStr">
         <is>
           <t>Taken as the last historical value</t>
@@ -2227,7 +2136,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Caprines % excretion in the barn as slurry</t>
+          <t>Caprines % excretion in the barn as other manure</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2235,8 +2144,6 @@
           <t>%</t>
         </is>
       </c>
-      <c r="C30" t="inlineStr"/>
-      <c r="D30" t="inlineStr"/>
       <c r="E30" t="inlineStr">
         <is>
           <t>Taken as the last historical value</t>
@@ -2246,7 +2153,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Porcines % excretion on grassland</t>
+          <t>Caprines % excretion in the barn as slurry</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2254,8 +2161,6 @@
           <t>%</t>
         </is>
       </c>
-      <c r="C31" t="inlineStr"/>
-      <c r="D31" t="inlineStr"/>
       <c r="E31" t="inlineStr">
         <is>
           <t>Taken as the last historical value</t>
@@ -2265,7 +2170,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Porcines % excretion in the barn as litter manure</t>
+          <t>Porcines % excretion on grassland</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2273,8 +2178,6 @@
           <t>%</t>
         </is>
       </c>
-      <c r="C32" t="inlineStr"/>
-      <c r="D32" t="inlineStr"/>
       <c r="E32" t="inlineStr">
         <is>
           <t>Taken as the last historical value</t>
@@ -2284,7 +2187,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Porcines % excretion in the barn as other manure</t>
+          <t>Porcines % excretion in the barn as litter manure</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2292,8 +2195,6 @@
           <t>%</t>
         </is>
       </c>
-      <c r="C33" t="inlineStr"/>
-      <c r="D33" t="inlineStr"/>
       <c r="E33" t="inlineStr">
         <is>
           <t>Taken as the last historical value</t>
@@ -2303,7 +2204,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Porcines % excretion in the barn as slurry</t>
+          <t>Porcines % excretion in the barn as other manure</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2311,8 +2212,6 @@
           <t>%</t>
         </is>
       </c>
-      <c r="C34" t="inlineStr"/>
-      <c r="D34" t="inlineStr"/>
       <c r="E34" t="inlineStr">
         <is>
           <t>Taken as the last historical value</t>
@@ -2322,7 +2221,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Poultry % excretion on grassland</t>
+          <t>Porcines % excretion in the barn as slurry</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2330,8 +2229,6 @@
           <t>%</t>
         </is>
       </c>
-      <c r="C35" t="inlineStr"/>
-      <c r="D35" t="inlineStr"/>
       <c r="E35" t="inlineStr">
         <is>
           <t>Taken as the last historical value</t>
@@ -2341,7 +2238,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Poultry % excretion in the barn as litter manure</t>
+          <t>Poultry % excretion on grassland</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2349,8 +2246,6 @@
           <t>%</t>
         </is>
       </c>
-      <c r="C36" t="inlineStr"/>
-      <c r="D36" t="inlineStr"/>
       <c r="E36" t="inlineStr">
         <is>
           <t>Taken as the last historical value</t>
@@ -2360,7 +2255,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Poultry % excretion in the barn as other manure</t>
+          <t>Poultry % excretion in the barn as litter manure</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2368,8 +2263,6 @@
           <t>%</t>
         </is>
       </c>
-      <c r="C37" t="inlineStr"/>
-      <c r="D37" t="inlineStr"/>
       <c r="E37" t="inlineStr">
         <is>
           <t>Taken as the last historical value</t>
@@ -2379,7 +2272,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Poultry % excretion in the barn as slurry</t>
+          <t>Poultry % excretion in the barn as other manure</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2387,8 +2280,6 @@
           <t>%</t>
         </is>
       </c>
-      <c r="C38" t="inlineStr"/>
-      <c r="D38" t="inlineStr"/>
       <c r="E38" t="inlineStr">
         <is>
           <t>Taken as the last historical value</t>
@@ -2398,16 +2289,14 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Bovines LU</t>
+          <t>Poultry % excretion in the barn as slurry</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>prop</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr"/>
-      <c r="D39" t="inlineStr"/>
+          <t>%</t>
+        </is>
+      </c>
       <c r="E39" t="inlineStr">
         <is>
           <t>Taken as the last historical value</t>
@@ -2417,7 +2306,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Ovines LU</t>
+          <t>Bovines LU</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2425,8 +2314,6 @@
           <t>prop</t>
         </is>
       </c>
-      <c r="C40" t="inlineStr"/>
-      <c r="D40" t="inlineStr"/>
       <c r="E40" t="inlineStr">
         <is>
           <t>Taken as the last historical value</t>
@@ -2436,7 +2323,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Caprines LU</t>
+          <t>Ovines LU</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -2444,8 +2331,6 @@
           <t>prop</t>
         </is>
       </c>
-      <c r="C41" t="inlineStr"/>
-      <c r="D41" t="inlineStr"/>
       <c r="E41" t="inlineStr">
         <is>
           <t>Taken as the last historical value</t>
@@ -2455,7 +2340,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Equines LU</t>
+          <t>Caprines LU</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -2463,8 +2348,6 @@
           <t>prop</t>
         </is>
       </c>
-      <c r="C42" t="inlineStr"/>
-      <c r="D42" t="inlineStr"/>
       <c r="E42" t="inlineStr">
         <is>
           <t>Taken as the last historical value</t>
@@ -2474,7 +2357,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Porcines LU</t>
+          <t>Equines LU</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -2482,8 +2365,6 @@
           <t>prop</t>
         </is>
       </c>
-      <c r="C43" t="inlineStr"/>
-      <c r="D43" t="inlineStr"/>
       <c r="E43" t="inlineStr">
         <is>
           <t>Taken as the last historical value</t>
@@ -2493,7 +2374,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Poultry LU</t>
+          <t>Porcines LU</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -2501,8 +2382,6 @@
           <t>prop</t>
         </is>
       </c>
-      <c r="C44" t="inlineStr"/>
-      <c r="D44" t="inlineStr"/>
       <c r="E44" t="inlineStr">
         <is>
           <t>Taken as the last historical value</t>
@@ -2512,26 +2391,24 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Bovines productivity</t>
+          <t>Poultry LU</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>kgcarcass/LU</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr"/>
-      <c r="D45" t="inlineStr"/>
+          <t>prop</t>
+        </is>
+      </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>These groups are taken as a whole even if only a part is producing meat, milk or eggs. Taken as the last historical value</t>
+          <t>Taken as the last historical value</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Ovines productivity</t>
+          <t>Bovines productivity</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -2539,8 +2416,6 @@
           <t>kgcarcass/LU</t>
         </is>
       </c>
-      <c r="C46" t="inlineStr"/>
-      <c r="D46" t="inlineStr"/>
       <c r="E46" t="inlineStr">
         <is>
           <t>These groups are taken as a whole even if only a part is producing meat, milk or eggs. Taken as the last historical value</t>
@@ -2550,7 +2425,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Caprines productivity</t>
+          <t>Ovines productivity</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -2558,8 +2433,6 @@
           <t>kgcarcass/LU</t>
         </is>
       </c>
-      <c r="C47" t="inlineStr"/>
-      <c r="D47" t="inlineStr"/>
       <c r="E47" t="inlineStr">
         <is>
           <t>These groups are taken as a whole even if only a part is producing meat, milk or eggs. Taken as the last historical value</t>
@@ -2569,7 +2442,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Equines productivity</t>
+          <t>Caprines productivity</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2577,8 +2450,6 @@
           <t>kgcarcass/LU</t>
         </is>
       </c>
-      <c r="C48" t="inlineStr"/>
-      <c r="D48" t="inlineStr"/>
       <c r="E48" t="inlineStr">
         <is>
           <t>These groups are taken as a whole even if only a part is producing meat, milk or eggs. Taken as the last historical value</t>
@@ -2588,7 +2459,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Porcines productivity</t>
+          <t>Equines productivity</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2596,8 +2467,6 @@
           <t>kgcarcass/LU</t>
         </is>
       </c>
-      <c r="C49" t="inlineStr"/>
-      <c r="D49" t="inlineStr"/>
       <c r="E49" t="inlineStr">
         <is>
           <t>These groups are taken as a whole even if only a part is producing meat, milk or eggs. Taken as the last historical value</t>
@@ -2607,7 +2476,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Poultry productivity</t>
+          <t>Porcines productivity</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -2615,8 +2484,6 @@
           <t>kgcarcass/LU</t>
         </is>
       </c>
-      <c r="C50" t="inlineStr"/>
-      <c r="D50" t="inlineStr"/>
       <c r="E50" t="inlineStr">
         <is>
           <t>These groups are taken as a whole even if only a part is producing meat, milk or eggs. Taken as the last historical value</t>
@@ -2626,16 +2493,14 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Bovines dairy productivity</t>
+          <t>Poultry productivity</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>kg/LU</t>
-        </is>
-      </c>
-      <c r="C51" t="inlineStr"/>
-      <c r="D51" t="inlineStr"/>
+          <t>kgcarcass/LU</t>
+        </is>
+      </c>
       <c r="E51" t="inlineStr">
         <is>
           <t>These groups are taken as a whole even if only a part is producing meat, milk or eggs. Taken as the last historical value</t>
@@ -2645,7 +2510,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Ovines dairy productivity</t>
+          <t>Bovines dairy productivity</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -2653,8 +2518,6 @@
           <t>kg/LU</t>
         </is>
       </c>
-      <c r="C52" t="inlineStr"/>
-      <c r="D52" t="inlineStr"/>
       <c r="E52" t="inlineStr">
         <is>
           <t>These groups are taken as a whole even if only a part is producing meat, milk or eggs. Taken as the last historical value</t>
@@ -2664,7 +2527,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Caprines dairy productivity</t>
+          <t>Ovines dairy productivity</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -2672,8 +2535,6 @@
           <t>kg/LU</t>
         </is>
       </c>
-      <c r="C53" t="inlineStr"/>
-      <c r="D53" t="inlineStr"/>
       <c r="E53" t="inlineStr">
         <is>
           <t>These groups are taken as a whole even if only a part is producing meat, milk or eggs. Taken as the last historical value</t>
@@ -2683,17 +2544,32 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
+          <t>Caprines dairy productivity</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>kg/LU</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>These groups are taken as a whole even if only a part is producing meat, milk or eggs. Taken as the last historical value</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
           <t>Poultry dairy productivity</t>
         </is>
       </c>
-      <c r="B54" t="inlineStr">
+      <c r="B55" t="inlineStr">
         <is>
           <t>kg/LU</t>
         </is>
       </c>
-      <c r="C54" t="inlineStr"/>
-      <c r="D54" t="inlineStr"/>
-      <c r="E54" t="inlineStr">
+      <c r="E55" t="inlineStr">
         <is>
           <t>These groups are taken as a whole even if only a part is producing meat, milk or eggs. Taken as the last historical value</t>
         </is>

--- a/src/grafs_e/data/scenario_region/Linear/Loire aval.xlsx
+++ b/src/grafs_e/data/scenario_region/Linear/Loire aval.xlsx
@@ -443,7 +443,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
@@ -465,7 +464,6 @@
         </is>
       </c>
     </row>
-    <row r="6"/>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
@@ -494,7 +492,6 @@
         </is>
       </c>
     </row>
-    <row r="11"/>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
@@ -502,7 +499,6 @@
         </is>
       </c>
     </row>
-    <row r="13"/>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
@@ -510,7 +506,6 @@
         </is>
       </c>
     </row>
-    <row r="15"/>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
@@ -555,7 +550,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E13"/>
+  <dimension ref="A1:E14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -786,6 +781,23 @@
       <c r="E13" t="inlineStr">
         <is>
           <t>No business as usual: computed with optimization model to fertilize all crops</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Methanisation</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>GWh</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>2021 data. Used as a goal but may be adjusted according to territory situation</t>
         </is>
       </c>
     </row>
@@ -1635,7 +1647,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E55"/>
+  <dimension ref="A1:E57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1672,7 +1684,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -1728,41 +1740,37 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>N recycling rate of human excretion in urban area</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>%</t>
-        </is>
+          <t>Weight export</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>2</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Taken as the last historical value</t>
+          <t>Weight for the optimization model</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>N recycling rate of human excretion in rural area</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>%</t>
-        </is>
+          <t>Weight energy</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>2</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Taken as the last historical value</t>
+          <t>Weight for the optimization model</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>NH3 volatilization coefficient for synthetic nitrogen</t>
+          <t>N recycling rate of human excretion in urban area</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1779,7 +1787,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Indirect N2O volatilization coefficient for synthetic nitrogen</t>
+          <t>N recycling rate of human excretion in rural area</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1796,41 +1804,41 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>kgN excreted by bovines LU</t>
+          <t>NH3 volatilization coefficient for synthetic nitrogen</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>kgN</t>
+          <t>%</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Historical trend</t>
+          <t>Taken as the last historical value</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>kgN excreted by equines LU</t>
+          <t>Indirect N2O volatilization coefficient for synthetic nitrogen</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>kgN</t>
+          <t>%</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Historical trend</t>
+          <t>Taken as the last historical value</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>kgN excreted by caprines LU</t>
+          <t>kgN excreted by bovines LU</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1847,7 +1855,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>kgN excreted by ovines LU</t>
+          <t>kgN excreted by equines LU</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1864,7 +1872,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>kgN excreted by porcines LU</t>
+          <t>kgN excreted by caprines LU</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1881,7 +1889,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>kgN excreted by poultry LU</t>
+          <t>kgN excreted by ovines LU</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1898,41 +1906,41 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Bovines % excretion on grassland</t>
+          <t>kgN excreted by porcines LU</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>%</t>
+          <t>kgN</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Taken as the last historical value</t>
+          <t>Historical trend</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Bovines % excretion in the barn as litter manure</t>
+          <t>kgN excreted by poultry LU</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>%</t>
+          <t>kgN</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Taken as the last historical value</t>
+          <t>Historical trend</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Bovines % excretion in the barn as other manure</t>
+          <t>Bovines % excretion on grassland</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1949,7 +1957,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Bovines % excretion in the barn as slurry</t>
+          <t>Bovines % excretion in the barn as litter manure</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1966,7 +1974,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Ovines % excretion on grassland</t>
+          <t>Bovines % excretion in the barn as other manure</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1983,7 +1991,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Ovines % excretion in the barn as litter manure</t>
+          <t>Bovines % excretion in the barn as slurry</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2000,7 +2008,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Ovines % excretion in the barn as other manure</t>
+          <t>Ovines % excretion on grassland</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2017,7 +2025,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Ovines % excretion in the barn as slurry</t>
+          <t>Ovines % excretion in the barn as litter manure</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2034,7 +2042,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Equines % excretion on grassland</t>
+          <t>Ovines % excretion in the barn as other manure</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2051,7 +2059,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Equines % excretion in the barn as litter manure</t>
+          <t>Ovines % excretion in the barn as slurry</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2068,7 +2076,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Equines % excretion in the barn as other manure</t>
+          <t>Equines % excretion on grassland</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2085,7 +2093,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Equines % excretion in the barn as slurry</t>
+          <t>Equines % excretion in the barn as litter manure</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2102,7 +2110,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Caprines % excretion on grassland</t>
+          <t>Equines % excretion in the barn as other manure</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2119,7 +2127,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Caprines % excretion in the barn as litter manure</t>
+          <t>Equines % excretion in the barn as slurry</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2136,7 +2144,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Caprines % excretion in the barn as other manure</t>
+          <t>Caprines % excretion on grassland</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2153,7 +2161,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Caprines % excretion in the barn as slurry</t>
+          <t>Caprines % excretion in the barn as litter manure</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2170,7 +2178,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Porcines % excretion on grassland</t>
+          <t>Caprines % excretion in the barn as other manure</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2187,7 +2195,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Porcines % excretion in the barn as litter manure</t>
+          <t>Caprines % excretion in the barn as slurry</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2204,7 +2212,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Porcines % excretion in the barn as other manure</t>
+          <t>Porcines % excretion on grassland</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2221,7 +2229,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Porcines % excretion in the barn as slurry</t>
+          <t>Porcines % excretion in the barn as litter manure</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2238,7 +2246,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Poultry % excretion on grassland</t>
+          <t>Porcines % excretion in the barn as other manure</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2255,7 +2263,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Poultry % excretion in the barn as litter manure</t>
+          <t>Porcines % excretion in the barn as slurry</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2272,7 +2280,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Poultry % excretion in the barn as other manure</t>
+          <t>Poultry % excretion on grassland</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2289,7 +2297,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Poultry % excretion in the barn as slurry</t>
+          <t>Poultry % excretion in the barn as litter manure</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2306,12 +2314,12 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Bovines LU</t>
+          <t>Poultry % excretion in the barn as other manure</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>prop</t>
+          <t>%</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -2323,12 +2331,12 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Ovines LU</t>
+          <t>Poultry % excretion in the barn as slurry</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>prop</t>
+          <t>%</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -2340,7 +2348,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Caprines LU</t>
+          <t>Bovines LU</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -2357,7 +2365,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Equines LU</t>
+          <t>Ovines LU</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -2374,7 +2382,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Porcines LU</t>
+          <t>Caprines LU</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -2391,7 +2399,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Poultry LU</t>
+          <t>Equines LU</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -2408,41 +2416,41 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Bovines productivity</t>
+          <t>Porcines LU</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>kgcarcass/LU</t>
+          <t>prop</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>These groups are taken as a whole even if only a part is producing meat, milk or eggs. Taken as the last historical value</t>
+          <t>Taken as the last historical value</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Ovines productivity</t>
+          <t>Poultry LU</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>kgcarcass/LU</t>
+          <t>prop</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>These groups are taken as a whole even if only a part is producing meat, milk or eggs. Taken as the last historical value</t>
+          <t>Taken as the last historical value</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Caprines productivity</t>
+          <t>Bovines productivity</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2459,7 +2467,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Equines productivity</t>
+          <t>Ovines productivity</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2476,7 +2484,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Porcines productivity</t>
+          <t>Caprines productivity</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -2493,7 +2501,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Poultry productivity</t>
+          <t>Equines productivity</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -2510,12 +2518,12 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Bovines dairy productivity</t>
+          <t>Porcines productivity</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>kg/LU</t>
+          <t>kgcarcass/LU</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -2527,12 +2535,12 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Ovines dairy productivity</t>
+          <t>Poultry productivity</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>kg/LU</t>
+          <t>kgcarcass/LU</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -2544,7 +2552,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Caprines dairy productivity</t>
+          <t>Bovines dairy productivity</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -2561,15 +2569,49 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
+          <t>Ovines dairy productivity</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>kg/LU</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>These groups are taken as a whole even if only a part is producing meat, milk or eggs. Taken as the last historical value</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>Caprines dairy productivity</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>kg/LU</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>These groups are taken as a whole even if only a part is producing meat, milk or eggs. Taken as the last historical value</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
           <t>Poultry dairy productivity</t>
         </is>
       </c>
-      <c r="B55" t="inlineStr">
+      <c r="B57" t="inlineStr">
         <is>
           <t>kg/LU</t>
         </is>
       </c>
-      <c r="E55" t="inlineStr">
+      <c r="E57" t="inlineStr">
         <is>
           <t>These groups are taken as a whole even if only a part is producing meat, milk or eggs. Taken as the last historical value</t>
         </is>

--- a/src/grafs_e/data/scenario_region/Linear/Loire aval.xlsx
+++ b/src/grafs_e/data/scenario_region/Linear/Loire aval.xlsx
@@ -443,7 +443,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
@@ -465,7 +464,6 @@
         </is>
       </c>
     </row>
-    <row r="6"/>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
@@ -494,7 +492,6 @@
         </is>
       </c>
     </row>
-    <row r="11"/>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
@@ -502,7 +499,6 @@
         </is>
       </c>
     </row>
-    <row r="13"/>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
@@ -510,7 +506,6 @@
         </is>
       </c>
     </row>
-    <row r="15"/>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
@@ -555,7 +550,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E13"/>
+  <dimension ref="A1:E14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -786,6 +781,23 @@
       <c r="E13" t="inlineStr">
         <is>
           <t>No business as usual: computed with optimization model to fertilize all crops</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Methaniser production</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>GWh/yr</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Regional 2021 data mapped on 2006 33 region plant production. Used as a goal but may be adjusted according to territory situation</t>
         </is>
       </c>
     </row>
@@ -1635,7 +1647,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E55"/>
+  <dimension ref="A1:E56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1672,7 +1684,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -1728,24 +1740,22 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>N recycling rate of human excretion in urban area</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>%</t>
-        </is>
+          <t>Weight energy</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>1</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Taken as the last historical value</t>
+          <t>Weight for the optimization model</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>N recycling rate of human excretion in rural area</t>
+          <t>N recycling rate of human excretion in urban area</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1762,7 +1772,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>NH3 volatilization coefficient for synthetic nitrogen</t>
+          <t>N recycling rate of human excretion in rural area</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1779,7 +1789,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Indirect N2O volatilization coefficient for synthetic nitrogen</t>
+          <t>NH3 volatilization coefficient for synthetic nitrogen</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1796,24 +1806,24 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>kgN excreted by bovines LU</t>
+          <t>Indirect N2O volatilization coefficient for synthetic nitrogen</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>kgN</t>
+          <t>%</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Historical trend</t>
+          <t>Taken as the last historical value</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>kgN excreted by equines LU</t>
+          <t>kgN excreted by bovines LU</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1830,7 +1840,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>kgN excreted by caprines LU</t>
+          <t>kgN excreted by equines LU</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1847,7 +1857,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>kgN excreted by ovines LU</t>
+          <t>kgN excreted by caprines LU</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1864,7 +1874,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>kgN excreted by porcines LU</t>
+          <t>kgN excreted by ovines LU</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1881,7 +1891,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>kgN excreted by poultry LU</t>
+          <t>kgN excreted by porcines LU</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1898,24 +1908,24 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Bovines % excretion on grassland</t>
+          <t>kgN excreted by poultry LU</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>%</t>
+          <t>kgN</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Taken as the last historical value</t>
+          <t>Historical trend</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Bovines % excretion in the barn as litter manure</t>
+          <t>Bovines % excretion on grassland</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1932,7 +1942,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Bovines % excretion in the barn as other manure</t>
+          <t>Bovines % excretion in the barn as litter manure</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1949,7 +1959,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Bovines % excretion in the barn as slurry</t>
+          <t>Bovines % excretion in the barn as other manure</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1966,7 +1976,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Ovines % excretion on grassland</t>
+          <t>Bovines % excretion in the barn as slurry</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1983,7 +1993,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Ovines % excretion in the barn as litter manure</t>
+          <t>Ovines % excretion on grassland</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2000,7 +2010,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Ovines % excretion in the barn as other manure</t>
+          <t>Ovines % excretion in the barn as litter manure</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2017,7 +2027,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Ovines % excretion in the barn as slurry</t>
+          <t>Ovines % excretion in the barn as other manure</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2034,7 +2044,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Equines % excretion on grassland</t>
+          <t>Ovines % excretion in the barn as slurry</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2051,7 +2061,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Equines % excretion in the barn as litter manure</t>
+          <t>Equines % excretion on grassland</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2068,7 +2078,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Equines % excretion in the barn as other manure</t>
+          <t>Equines % excretion in the barn as litter manure</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2085,7 +2095,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Equines % excretion in the barn as slurry</t>
+          <t>Equines % excretion in the barn as other manure</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2102,7 +2112,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Caprines % excretion on grassland</t>
+          <t>Equines % excretion in the barn as slurry</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2119,7 +2129,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Caprines % excretion in the barn as litter manure</t>
+          <t>Caprines % excretion on grassland</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2136,7 +2146,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Caprines % excretion in the barn as other manure</t>
+          <t>Caprines % excretion in the barn as litter manure</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2153,7 +2163,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Caprines % excretion in the barn as slurry</t>
+          <t>Caprines % excretion in the barn as other manure</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2170,7 +2180,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Porcines % excretion on grassland</t>
+          <t>Caprines % excretion in the barn as slurry</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2187,7 +2197,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Porcines % excretion in the barn as litter manure</t>
+          <t>Porcines % excretion on grassland</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2204,7 +2214,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Porcines % excretion in the barn as other manure</t>
+          <t>Porcines % excretion in the barn as litter manure</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2221,7 +2231,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Porcines % excretion in the barn as slurry</t>
+          <t>Porcines % excretion in the barn as other manure</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2238,7 +2248,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Poultry % excretion on grassland</t>
+          <t>Porcines % excretion in the barn as slurry</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2255,7 +2265,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Poultry % excretion in the barn as litter manure</t>
+          <t>Poultry % excretion on grassland</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2272,7 +2282,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Poultry % excretion in the barn as other manure</t>
+          <t>Poultry % excretion in the barn as litter manure</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2289,7 +2299,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Poultry % excretion in the barn as slurry</t>
+          <t>Poultry % excretion in the barn as other manure</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2306,12 +2316,12 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Bovines LU</t>
+          <t>Poultry % excretion in the barn as slurry</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>prop</t>
+          <t>%</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -2323,7 +2333,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Ovines LU</t>
+          <t>Bovines LU</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -2340,7 +2350,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Caprines LU</t>
+          <t>Ovines LU</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -2357,7 +2367,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Equines LU</t>
+          <t>Caprines LU</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -2374,7 +2384,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Porcines LU</t>
+          <t>Equines LU</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -2391,7 +2401,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Poultry LU</t>
+          <t>Porcines LU</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -2408,24 +2418,24 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Bovines productivity</t>
+          <t>Poultry LU</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>kgcarcass/LU</t>
+          <t>prop</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>These groups are taken as a whole even if only a part is producing meat, milk or eggs. Taken as the last historical value</t>
+          <t>Taken as the last historical value</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Ovines productivity</t>
+          <t>Bovines productivity</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -2442,7 +2452,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Caprines productivity</t>
+          <t>Ovines productivity</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2459,7 +2469,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Equines productivity</t>
+          <t>Caprines productivity</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2476,7 +2486,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Porcines productivity</t>
+          <t>Equines productivity</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -2493,7 +2503,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Poultry productivity</t>
+          <t>Porcines productivity</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -2510,12 +2520,12 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Bovines dairy productivity</t>
+          <t>Poultry productivity</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>kg/LU</t>
+          <t>kgcarcass/LU</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -2527,7 +2537,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Ovines dairy productivity</t>
+          <t>Bovines dairy productivity</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -2544,7 +2554,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Caprines dairy productivity</t>
+          <t>Ovines dairy productivity</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -2561,15 +2571,32 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
+          <t>Caprines dairy productivity</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>kg/LU</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>These groups are taken as a whole even if only a part is producing meat, milk or eggs. Taken as the last historical value</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
           <t>Poultry dairy productivity</t>
         </is>
       </c>
-      <c r="B55" t="inlineStr">
+      <c r="B56" t="inlineStr">
         <is>
           <t>kg/LU</t>
         </is>
       </c>
-      <c r="E55" t="inlineStr">
+      <c r="E56" t="inlineStr">
         <is>
           <t>These groups are taken as a whole even if only a part is producing meat, milk or eggs. Taken as the last historical value</t>
         </is>

--- a/src/grafs_e/data/scenario_region/Linear/Loire aval.xlsx
+++ b/src/grafs_e/data/scenario_region/Linear/Loire aval.xlsx
@@ -1647,7 +1647,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E56"/>
+  <dimension ref="A1:E62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1755,24 +1755,22 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>N recycling rate of human excretion in urban area</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>%</t>
-        </is>
+          <t>Weight methaniser input</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>25</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Taken as the last historical value</t>
+          <t>Weight for the optimization model</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>N recycling rate of human excretion in rural area</t>
+          <t>N recycling rate of human excretion in urban area</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1789,7 +1787,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>NH3 volatilization coefficient for synthetic nitrogen</t>
+          <t>N recycling rate of human excretion in rural area</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1806,7 +1804,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Indirect N2O volatilization coefficient for synthetic nitrogen</t>
+          <t>NH3 volatilization coefficient for synthetic nitrogen</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1823,24 +1821,24 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>kgN excreted by bovines LU</t>
+          <t>Indirect N2O volatilization coefficient for synthetic nitrogen</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>kgN</t>
+          <t>%</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Historical trend</t>
+          <t>Taken as the last historical value</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>kgN excreted by equines LU</t>
+          <t>kgN excreted by bovines LU</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1857,7 +1855,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>kgN excreted by caprines LU</t>
+          <t>kgN excreted by equines LU</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1874,7 +1872,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>kgN excreted by ovines LU</t>
+          <t>kgN excreted by caprines LU</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1891,7 +1889,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>kgN excreted by porcines LU</t>
+          <t>kgN excreted by ovines LU</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1908,7 +1906,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>kgN excreted by poultry LU</t>
+          <t>kgN excreted by porcines LU</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1925,24 +1923,24 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Bovines % excretion on grassland</t>
+          <t>kgN excreted by poultry LU</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>%</t>
+          <t>kgN</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Taken as the last historical value</t>
+          <t>Historical trend</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Bovines % excretion in the barn as litter manure</t>
+          <t>Bovines % excretion on grassland</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1959,7 +1957,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Bovines % excretion in the barn as other manure</t>
+          <t>Bovines % excretion in the barn as litter manure</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1976,7 +1974,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Bovines % excretion in the barn as slurry</t>
+          <t>Bovines % excretion in the barn as other manure</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1993,7 +1991,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Ovines % excretion on grassland</t>
+          <t>Bovines % excretion in the barn as slurry</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2010,7 +2008,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Ovines % excretion in the barn as litter manure</t>
+          <t>Ovines % excretion on grassland</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2027,7 +2025,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Ovines % excretion in the barn as other manure</t>
+          <t>Ovines % excretion in the barn as litter manure</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2044,7 +2042,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Ovines % excretion in the barn as slurry</t>
+          <t>Ovines % excretion in the barn as other manure</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2061,7 +2059,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Equines % excretion on grassland</t>
+          <t>Ovines % excretion in the barn as slurry</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2078,7 +2076,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Equines % excretion in the barn as litter manure</t>
+          <t>Equines % excretion on grassland</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2095,7 +2093,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Equines % excretion in the barn as other manure</t>
+          <t>Equines % excretion in the barn as litter manure</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2112,7 +2110,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Equines % excretion in the barn as slurry</t>
+          <t>Equines % excretion in the barn as other manure</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2129,7 +2127,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Caprines % excretion on grassland</t>
+          <t>Equines % excretion in the barn as slurry</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2146,7 +2144,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Caprines % excretion in the barn as litter manure</t>
+          <t>Caprines % excretion on grassland</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2163,7 +2161,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Caprines % excretion in the barn as other manure</t>
+          <t>Caprines % excretion in the barn as litter manure</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2180,7 +2178,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Caprines % excretion in the barn as slurry</t>
+          <t>Caprines % excretion in the barn as other manure</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2197,7 +2195,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Porcines % excretion on grassland</t>
+          <t>Caprines % excretion in the barn as slurry</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2214,7 +2212,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Porcines % excretion in the barn as litter manure</t>
+          <t>Porcines % excretion on grassland</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2231,7 +2229,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Porcines % excretion in the barn as other manure</t>
+          <t>Porcines % excretion in the barn as litter manure</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2248,7 +2246,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Porcines % excretion in the barn as slurry</t>
+          <t>Porcines % excretion in the barn as other manure</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2265,7 +2263,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Poultry % excretion on grassland</t>
+          <t>Porcines % excretion in the barn as slurry</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2282,7 +2280,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Poultry % excretion in the barn as litter manure</t>
+          <t>Poultry % excretion on grassland</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2299,7 +2297,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Poultry % excretion in the barn as other manure</t>
+          <t>Poultry % excretion in the barn as litter manure</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2316,7 +2314,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Poultry % excretion in the barn as slurry</t>
+          <t>Poultry % excretion in the barn as other manure</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2333,12 +2331,12 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Bovines LU</t>
+          <t>Poultry % excretion in the barn as slurry</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>prop</t>
+          <t>%</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -2350,7 +2348,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Ovines LU</t>
+          <t>Bovines LU</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -2367,7 +2365,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Caprines LU</t>
+          <t>Ovines LU</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -2384,7 +2382,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Equines LU</t>
+          <t>Caprines LU</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -2401,7 +2399,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Porcines LU</t>
+          <t>Equines LU</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -2418,7 +2416,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Poultry LU</t>
+          <t>Porcines LU</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -2435,24 +2433,24 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Bovines productivity</t>
+          <t>Poultry LU</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>kgcarcass/LU</t>
+          <t>prop</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>These groups are taken as a whole even if only a part is producing meat, milk or eggs. Taken as the last historical value</t>
+          <t>Taken as the last historical value</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Ovines productivity</t>
+          <t>Bovines productivity</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2469,7 +2467,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Caprines productivity</t>
+          <t>Ovines productivity</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2486,7 +2484,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Equines productivity</t>
+          <t>Caprines productivity</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -2503,7 +2501,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Porcines productivity</t>
+          <t>Equines productivity</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -2520,7 +2518,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Poultry productivity</t>
+          <t>Porcines productivity</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -2537,12 +2535,12 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Bovines dairy productivity</t>
+          <t>Poultry productivity</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>kg/LU</t>
+          <t>kgcarcass/LU</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -2554,7 +2552,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Ovines dairy productivity</t>
+          <t>Bovines dairy productivity</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -2571,7 +2569,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Caprines dairy productivity</t>
+          <t>Ovines dairy productivity</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -2588,17 +2586,134 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
+          <t>Caprines dairy productivity</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>kg/LU</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>These groups are taken as a whole even if only a part is producing meat, milk or eggs. Taken as the last historical value</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
           <t>Poultry dairy productivity</t>
         </is>
       </c>
-      <c r="B56" t="inlineStr">
+      <c r="B57" t="inlineStr">
         <is>
           <t>kg/LU</t>
         </is>
       </c>
-      <c r="E56" t="inlineStr">
+      <c r="E57" t="inlineStr">
         <is>
           <t>These groups are taken as a whole even if only a part is producing meat, milk or eggs. Taken as the last historical value</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>Share of crop residues in methaniser</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>prop</t>
+        </is>
+      </c>
+      <c r="C58" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>Adapted from ONRB data</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>Share of green waste in methaniser</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>prop</t>
+        </is>
+      </c>
+      <c r="C59" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>Adapted from ONRB data</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>Share of dedicated culture in methaniser</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>prop</t>
+        </is>
+      </c>
+      <c r="C60" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>Adapted from ONRB data</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>Share of animal food industry in methaniser</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>prop</t>
+        </is>
+      </c>
+      <c r="C61" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>Adapted from ONRB data</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>Share of livestock effluent in methaniser</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>prop</t>
+        </is>
+      </c>
+      <c r="C62" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>Adapted from ONRB data</t>
         </is>
       </c>
     </row>

--- a/src/grafs_e/data/scenario_region/Linear/Loire aval.xlsx
+++ b/src/grafs_e/data/scenario_region/Linear/Loire aval.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="doc" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="main" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="area" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="technical" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="doc" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="main" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="area" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="technical" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -439,13 +439,9 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t> </t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr"/>
-      <c r="B2" t="inlineStr"/>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -453,7 +449,6 @@
           <t>create your scenario with basic data in main scenario tab. Add your scenario values in scenario column</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -461,7 +456,6 @@
           <t>if no value is given, the business as usual value will be used</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -469,11 +463,6 @@
           <t>if the territory requested is not found in the data, the business as usual column will be blank and you have to define all variables.</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr"/>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr"/>
-      <c r="B6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -481,7 +470,6 @@
           <t>Surface change tab is used to give general indication of crop rotation. This will give specific surface constraint for the model.</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -489,7 +477,6 @@
           <t>In culture field add the name of the culture and the scenario surface</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -497,7 +484,6 @@
           <t>You can enforce the given values by adding TRUE in the enforce column. Caution, if the sum of the enforced area is beyond total surface area, you will get an error.</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -505,11 +491,6 @@
           <t>For all culture not mentionned in the surface change tab, their surface will be deduced from previous historical data and scenario input</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr"/>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr"/>
-      <c r="B11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -517,11 +498,6 @@
           <t>Use technical scenario to change secondary parameters of the model</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr"/>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr"/>
-      <c r="B13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -529,11 +505,6 @@
           <t>BAU compute Business as usual scenario</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr"/>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr"/>
-      <c r="B15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -541,7 +512,6 @@
           <t>Scenario name</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -549,7 +519,6 @@
           <t>Region name</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -557,7 +526,6 @@
           <t>Year</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -582,31 +550,31 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E12"/>
+  <dimension ref="A1:E14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Variable</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>Unit</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>Business as usual</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Scenario</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>comment</t>
         </is>
@@ -623,8 +591,6 @@
           <t>M inhabitant</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr"/>
-      <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
           <t>INSEE data</t>
@@ -642,8 +608,6 @@
           <t>%</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr"/>
-      <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
           <t>Logistic</t>
@@ -661,8 +625,6 @@
           <t>kgN/cap/yr</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr"/>
-      <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
           <t>Taken as the last historical value</t>
@@ -680,8 +642,6 @@
           <t>kgN/cap/yr</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr"/>
-      <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
           <t>Taken as the last historical value</t>
@@ -699,8 +659,6 @@
           <t>kgN/cap/yr</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr"/>
-      <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
           <t>Taken as the last historical value</t>
@@ -718,8 +676,6 @@
           <t>ha</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr"/>
-      <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
           <t>Historical trend</t>
@@ -737,8 +693,6 @@
           <t>ha</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr"/>
-      <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
           <t>Historical trend</t>
@@ -748,7 +702,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Net import of vegetal pdcts</t>
+          <t>Import of vegetal pdcts</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -756,68 +710,94 @@
           <t>ktN</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr"/>
-      <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Historical trend. Used as a goal but may be adjusted according to territory situation</t>
+          <t>2006 data. Used as a goal but may be adjusted according to territory situation</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Total LU</t>
+          <t>Export of vegetal pdcts</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>LU</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr"/>
-      <c r="D10" t="inlineStr"/>
+          <t>ktN</t>
+        </is>
+      </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Historical trend, see prop for each livestock in technical sheet</t>
+          <t>2006 data. Used as a goal but may be adjusted according to territory situation</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Synth N fertilizer application to cropland</t>
+          <t>Total LU</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>kgN/ha/yr</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr"/>
-      <c r="D11" t="inlineStr"/>
+          <t>LU</t>
+        </is>
+      </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>No business as usual: computed with optimization model to fertilize all crops</t>
+          <t>Historical trend, see prop for each livestock in technical sheet</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
+          <t>Synth N fertilizer application to cropland</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>kgN/ha/yr</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>No business as usual: computed with optimization model to fertilize all crops</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
           <t>Synth N fertilizer application to grassland</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="B13" t="inlineStr">
         <is>
           <t>kgN/ha/yr</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr"/>
-      <c r="D12" t="inlineStr"/>
-      <c r="E12" t="inlineStr">
+      <c r="E13" t="inlineStr">
         <is>
           <t>No business as usual: computed with optimization model to fertilize all crops</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Methaniser production</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>GWh/yr</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Regional 2021 data mapped on 2006 33 region plant production. Used as a goal but may be adjusted according to territory situation</t>
         </is>
       </c>
     </row>
@@ -1643,7 +1623,6 @@
           <t xml:space="preserve">Natural meadow </t>
         </is>
       </c>
-      <c r="B37" t="inlineStr"/>
       <c r="C37" t="b">
         <v>0</v>
       </c>
@@ -1668,31 +1647,31 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E54"/>
+  <dimension ref="A1:E62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Variable</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>unit</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>Business as usual</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Scenario</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>Comment</t>
         </is>
@@ -1704,11 +1683,9 @@
           <t>Weight diet</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr"/>
       <c r="C2" t="n">
-        <v>1</v>
-      </c>
-      <c r="D2" t="inlineStr"/>
+        <v>10</v>
+      </c>
       <c r="E2" t="inlineStr">
         <is>
           <t>Weight for the optimization model</t>
@@ -1721,11 +1698,9 @@
           <t>Weight synthetic fertilizer use</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr"/>
       <c r="C3" t="n">
         <v>5</v>
       </c>
-      <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
           <t>Weight for the optimization model</t>
@@ -1735,14 +1710,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Weight import/export balance</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr"/>
+          <t>Weight import</t>
+        </is>
+      </c>
       <c r="C4" t="n">
         <v>2</v>
       </c>
-      <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
           <t>Weight for the optimization model</t>
@@ -1752,64 +1725,52 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>N recycling rate of human excretion in urban area</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>%</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr"/>
-      <c r="D5" t="inlineStr"/>
+          <t>Weight export</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>2</v>
+      </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Taken as the last historical value</t>
+          <t>Weight for the optimization model</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>N recycling rate of human excretion in rural area</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>%</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr"/>
-      <c r="D6" t="inlineStr"/>
+          <t>Weight energy</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>1</v>
+      </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Taken as the last historical value</t>
+          <t>Weight for the optimization model</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>NH3 volatilization coefficient for synthetic nitrogen</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>%</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr"/>
-      <c r="D7" t="inlineStr"/>
+          <t>Weight methaniser input</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>25</v>
+      </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Taken as the last historical value</t>
+          <t>Weight for the optimization model</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Indirect N2O volatilization coefficient for synthetic nitrogen</t>
+          <t>N recycling rate of human excretion in urban area</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1817,8 +1778,6 @@
           <t>%</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr"/>
-      <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
           <t>Taken as the last historical value</t>
@@ -1828,64 +1787,58 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>kgN excreted by bovines LU</t>
+          <t>N recycling rate of human excretion in rural area</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>kgN</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr"/>
-      <c r="D9" t="inlineStr"/>
+          <t>%</t>
+        </is>
+      </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Historical trend</t>
+          <t>Taken as the last historical value</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>kgN excreted by equines LU</t>
+          <t>NH3 volatilization coefficient for synthetic nitrogen</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>kgN</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr"/>
-      <c r="D10" t="inlineStr"/>
+          <t>%</t>
+        </is>
+      </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Historical trend</t>
+          <t>Taken as the last historical value</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>kgN excreted by caprines LU</t>
+          <t>Indirect N2O volatilization coefficient for synthetic nitrogen</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>kgN</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr"/>
-      <c r="D11" t="inlineStr"/>
+          <t>%</t>
+        </is>
+      </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Historical trend</t>
+          <t>Taken as the last historical value</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>kgN excreted by ovines LU</t>
+          <t>kgN excreted by bovines LU</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1893,8 +1846,6 @@
           <t>kgN</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr"/>
-      <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
           <t>Historical trend</t>
@@ -1904,7 +1855,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>kgN excreted by porcines LU</t>
+          <t>kgN excreted by equines LU</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1912,8 +1863,6 @@
           <t>kgN</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr"/>
-      <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
         <is>
           <t>Historical trend</t>
@@ -1923,7 +1872,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>kgN excreted by poultry LU</t>
+          <t>kgN excreted by caprines LU</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1931,8 +1880,6 @@
           <t>kgN</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr"/>
-      <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr">
         <is>
           <t>Historical trend</t>
@@ -1942,64 +1889,58 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Bovines % excretion on grassland</t>
+          <t>kgN excreted by ovines LU</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>%</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr"/>
-      <c r="D15" t="inlineStr"/>
+          <t>kgN</t>
+        </is>
+      </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Taken as the last historical value</t>
+          <t>Historical trend</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Bovines % excretion in the barn as litter manure</t>
+          <t>kgN excreted by porcines LU</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>%</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr"/>
-      <c r="D16" t="inlineStr"/>
+          <t>kgN</t>
+        </is>
+      </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Taken as the last historical value</t>
+          <t>Historical trend</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Bovines % excretion in the barn as other manure</t>
+          <t>kgN excreted by poultry LU</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>%</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr"/>
-      <c r="D17" t="inlineStr"/>
+          <t>kgN</t>
+        </is>
+      </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Taken as the last historical value</t>
+          <t>Historical trend</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Bovines % excretion in the barn as slurry</t>
+          <t>Bovines % excretion on grassland</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2007,8 +1948,6 @@
           <t>%</t>
         </is>
       </c>
-      <c r="C18" t="inlineStr"/>
-      <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr">
         <is>
           <t>Taken as the last historical value</t>
@@ -2018,7 +1957,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Ovines % excretion on grassland</t>
+          <t>Bovines % excretion in the barn as litter manure</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2026,8 +1965,6 @@
           <t>%</t>
         </is>
       </c>
-      <c r="C19" t="inlineStr"/>
-      <c r="D19" t="inlineStr"/>
       <c r="E19" t="inlineStr">
         <is>
           <t>Taken as the last historical value</t>
@@ -2037,7 +1974,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Ovines % excretion in the barn as litter manure</t>
+          <t>Bovines % excretion in the barn as other manure</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2045,8 +1982,6 @@
           <t>%</t>
         </is>
       </c>
-      <c r="C20" t="inlineStr"/>
-      <c r="D20" t="inlineStr"/>
       <c r="E20" t="inlineStr">
         <is>
           <t>Taken as the last historical value</t>
@@ -2056,7 +1991,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Ovines % excretion in the barn as other manure</t>
+          <t>Bovines % excretion in the barn as slurry</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2064,8 +1999,6 @@
           <t>%</t>
         </is>
       </c>
-      <c r="C21" t="inlineStr"/>
-      <c r="D21" t="inlineStr"/>
       <c r="E21" t="inlineStr">
         <is>
           <t>Taken as the last historical value</t>
@@ -2075,7 +2008,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Ovines % excretion in the barn as slurry</t>
+          <t>Ovines % excretion on grassland</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2083,8 +2016,6 @@
           <t>%</t>
         </is>
       </c>
-      <c r="C22" t="inlineStr"/>
-      <c r="D22" t="inlineStr"/>
       <c r="E22" t="inlineStr">
         <is>
           <t>Taken as the last historical value</t>
@@ -2094,7 +2025,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Equines % excretion on grassland</t>
+          <t>Ovines % excretion in the barn as litter manure</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2102,8 +2033,6 @@
           <t>%</t>
         </is>
       </c>
-      <c r="C23" t="inlineStr"/>
-      <c r="D23" t="inlineStr"/>
       <c r="E23" t="inlineStr">
         <is>
           <t>Taken as the last historical value</t>
@@ -2113,7 +2042,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Equines % excretion in the barn as litter manure</t>
+          <t>Ovines % excretion in the barn as other manure</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2121,8 +2050,6 @@
           <t>%</t>
         </is>
       </c>
-      <c r="C24" t="inlineStr"/>
-      <c r="D24" t="inlineStr"/>
       <c r="E24" t="inlineStr">
         <is>
           <t>Taken as the last historical value</t>
@@ -2132,7 +2059,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Equines % excretion in the barn as other manure</t>
+          <t>Ovines % excretion in the barn as slurry</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2140,8 +2067,6 @@
           <t>%</t>
         </is>
       </c>
-      <c r="C25" t="inlineStr"/>
-      <c r="D25" t="inlineStr"/>
       <c r="E25" t="inlineStr">
         <is>
           <t>Taken as the last historical value</t>
@@ -2151,7 +2076,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Equines % excretion in the barn as slurry</t>
+          <t>Equines % excretion on grassland</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2159,8 +2084,6 @@
           <t>%</t>
         </is>
       </c>
-      <c r="C26" t="inlineStr"/>
-      <c r="D26" t="inlineStr"/>
       <c r="E26" t="inlineStr">
         <is>
           <t>Taken as the last historical value</t>
@@ -2170,7 +2093,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Caprines % excretion on grassland</t>
+          <t>Equines % excretion in the barn as litter manure</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2178,8 +2101,6 @@
           <t>%</t>
         </is>
       </c>
-      <c r="C27" t="inlineStr"/>
-      <c r="D27" t="inlineStr"/>
       <c r="E27" t="inlineStr">
         <is>
           <t>Taken as the last historical value</t>
@@ -2189,7 +2110,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Caprines % excretion in the barn as litter manure</t>
+          <t>Equines % excretion in the barn as other manure</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2197,8 +2118,6 @@
           <t>%</t>
         </is>
       </c>
-      <c r="C28" t="inlineStr"/>
-      <c r="D28" t="inlineStr"/>
       <c r="E28" t="inlineStr">
         <is>
           <t>Taken as the last historical value</t>
@@ -2208,7 +2127,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Caprines % excretion in the barn as other manure</t>
+          <t>Equines % excretion in the barn as slurry</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2216,8 +2135,6 @@
           <t>%</t>
         </is>
       </c>
-      <c r="C29" t="inlineStr"/>
-      <c r="D29" t="inlineStr"/>
       <c r="E29" t="inlineStr">
         <is>
           <t>Taken as the last historical value</t>
@@ -2227,7 +2144,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Caprines % excretion in the barn as slurry</t>
+          <t>Caprines % excretion on grassland</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2235,8 +2152,6 @@
           <t>%</t>
         </is>
       </c>
-      <c r="C30" t="inlineStr"/>
-      <c r="D30" t="inlineStr"/>
       <c r="E30" t="inlineStr">
         <is>
           <t>Taken as the last historical value</t>
@@ -2246,7 +2161,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Porcines % excretion on grassland</t>
+          <t>Caprines % excretion in the barn as litter manure</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2254,8 +2169,6 @@
           <t>%</t>
         </is>
       </c>
-      <c r="C31" t="inlineStr"/>
-      <c r="D31" t="inlineStr"/>
       <c r="E31" t="inlineStr">
         <is>
           <t>Taken as the last historical value</t>
@@ -2265,7 +2178,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Porcines % excretion in the barn as litter manure</t>
+          <t>Caprines % excretion in the barn as other manure</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2273,8 +2186,6 @@
           <t>%</t>
         </is>
       </c>
-      <c r="C32" t="inlineStr"/>
-      <c r="D32" t="inlineStr"/>
       <c r="E32" t="inlineStr">
         <is>
           <t>Taken as the last historical value</t>
@@ -2284,7 +2195,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Porcines % excretion in the barn as other manure</t>
+          <t>Caprines % excretion in the barn as slurry</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2292,8 +2203,6 @@
           <t>%</t>
         </is>
       </c>
-      <c r="C33" t="inlineStr"/>
-      <c r="D33" t="inlineStr"/>
       <c r="E33" t="inlineStr">
         <is>
           <t>Taken as the last historical value</t>
@@ -2303,7 +2212,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Porcines % excretion in the barn as slurry</t>
+          <t>Porcines % excretion on grassland</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2311,8 +2220,6 @@
           <t>%</t>
         </is>
       </c>
-      <c r="C34" t="inlineStr"/>
-      <c r="D34" t="inlineStr"/>
       <c r="E34" t="inlineStr">
         <is>
           <t>Taken as the last historical value</t>
@@ -2322,7 +2229,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Poultry % excretion on grassland</t>
+          <t>Porcines % excretion in the barn as litter manure</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2330,8 +2237,6 @@
           <t>%</t>
         </is>
       </c>
-      <c r="C35" t="inlineStr"/>
-      <c r="D35" t="inlineStr"/>
       <c r="E35" t="inlineStr">
         <is>
           <t>Taken as the last historical value</t>
@@ -2341,7 +2246,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Poultry % excretion in the barn as litter manure</t>
+          <t>Porcines % excretion in the barn as other manure</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2349,8 +2254,6 @@
           <t>%</t>
         </is>
       </c>
-      <c r="C36" t="inlineStr"/>
-      <c r="D36" t="inlineStr"/>
       <c r="E36" t="inlineStr">
         <is>
           <t>Taken as the last historical value</t>
@@ -2360,7 +2263,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Poultry % excretion in the barn as other manure</t>
+          <t>Porcines % excretion in the barn as slurry</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2368,8 +2271,6 @@
           <t>%</t>
         </is>
       </c>
-      <c r="C37" t="inlineStr"/>
-      <c r="D37" t="inlineStr"/>
       <c r="E37" t="inlineStr">
         <is>
           <t>Taken as the last historical value</t>
@@ -2379,7 +2280,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Poultry % excretion in the barn as slurry</t>
+          <t>Poultry % excretion on grassland</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2387,8 +2288,6 @@
           <t>%</t>
         </is>
       </c>
-      <c r="C38" t="inlineStr"/>
-      <c r="D38" t="inlineStr"/>
       <c r="E38" t="inlineStr">
         <is>
           <t>Taken as the last historical value</t>
@@ -2398,16 +2297,14 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Bovines LU</t>
+          <t>Poultry % excretion in the barn as litter manure</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>prop</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr"/>
-      <c r="D39" t="inlineStr"/>
+          <t>%</t>
+        </is>
+      </c>
       <c r="E39" t="inlineStr">
         <is>
           <t>Taken as the last historical value</t>
@@ -2417,16 +2314,14 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Ovines LU</t>
+          <t>Poultry % excretion in the barn as other manure</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>prop</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr"/>
-      <c r="D40" t="inlineStr"/>
+          <t>%</t>
+        </is>
+      </c>
       <c r="E40" t="inlineStr">
         <is>
           <t>Taken as the last historical value</t>
@@ -2436,16 +2331,14 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Caprines LU</t>
+          <t>Poultry % excretion in the barn as slurry</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>prop</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr"/>
-      <c r="D41" t="inlineStr"/>
+          <t>%</t>
+        </is>
+      </c>
       <c r="E41" t="inlineStr">
         <is>
           <t>Taken as the last historical value</t>
@@ -2455,7 +2348,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Equines LU</t>
+          <t>Bovines LU</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -2463,8 +2356,6 @@
           <t>prop</t>
         </is>
       </c>
-      <c r="C42" t="inlineStr"/>
-      <c r="D42" t="inlineStr"/>
       <c r="E42" t="inlineStr">
         <is>
           <t>Taken as the last historical value</t>
@@ -2474,7 +2365,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Porcines LU</t>
+          <t>Ovines LU</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -2482,8 +2373,6 @@
           <t>prop</t>
         </is>
       </c>
-      <c r="C43" t="inlineStr"/>
-      <c r="D43" t="inlineStr"/>
       <c r="E43" t="inlineStr">
         <is>
           <t>Taken as the last historical value</t>
@@ -2493,7 +2382,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Poultry LU</t>
+          <t>Caprines LU</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -2501,8 +2390,6 @@
           <t>prop</t>
         </is>
       </c>
-      <c r="C44" t="inlineStr"/>
-      <c r="D44" t="inlineStr"/>
       <c r="E44" t="inlineStr">
         <is>
           <t>Taken as the last historical value</t>
@@ -2512,64 +2399,58 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Bovines productivity</t>
+          <t>Equines LU</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>kgcarcass/LU</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr"/>
-      <c r="D45" t="inlineStr"/>
+          <t>prop</t>
+        </is>
+      </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>These groups are taken as a whole even if only a part is producing meat, milk or eggs. Taken as the last historical value</t>
+          <t>Taken as the last historical value</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Ovines productivity</t>
+          <t>Porcines LU</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>kgcarcass/LU</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr"/>
-      <c r="D46" t="inlineStr"/>
+          <t>prop</t>
+        </is>
+      </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>These groups are taken as a whole even if only a part is producing meat, milk or eggs. Taken as the last historical value</t>
+          <t>Taken as the last historical value</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Caprines productivity</t>
+          <t>Poultry LU</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>kgcarcass/LU</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr"/>
-      <c r="D47" t="inlineStr"/>
+          <t>prop</t>
+        </is>
+      </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>These groups are taken as a whole even if only a part is producing meat, milk or eggs. Taken as the last historical value</t>
+          <t>Taken as the last historical value</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Equines productivity</t>
+          <t>Bovines productivity</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2577,8 +2458,6 @@
           <t>kgcarcass/LU</t>
         </is>
       </c>
-      <c r="C48" t="inlineStr"/>
-      <c r="D48" t="inlineStr"/>
       <c r="E48" t="inlineStr">
         <is>
           <t>These groups are taken as a whole even if only a part is producing meat, milk or eggs. Taken as the last historical value</t>
@@ -2588,7 +2467,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Porcines productivity</t>
+          <t>Ovines productivity</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2596,8 +2475,6 @@
           <t>kgcarcass/LU</t>
         </is>
       </c>
-      <c r="C49" t="inlineStr"/>
-      <c r="D49" t="inlineStr"/>
       <c r="E49" t="inlineStr">
         <is>
           <t>These groups are taken as a whole even if only a part is producing meat, milk or eggs. Taken as the last historical value</t>
@@ -2607,7 +2484,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Poultry productivity</t>
+          <t>Caprines productivity</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -2615,8 +2492,6 @@
           <t>kgcarcass/LU</t>
         </is>
       </c>
-      <c r="C50" t="inlineStr"/>
-      <c r="D50" t="inlineStr"/>
       <c r="E50" t="inlineStr">
         <is>
           <t>These groups are taken as a whole even if only a part is producing meat, milk or eggs. Taken as the last historical value</t>
@@ -2626,16 +2501,14 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Bovines dairy productivity</t>
+          <t>Equines productivity</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>kg/LU</t>
-        </is>
-      </c>
-      <c r="C51" t="inlineStr"/>
-      <c r="D51" t="inlineStr"/>
+          <t>kgcarcass/LU</t>
+        </is>
+      </c>
       <c r="E51" t="inlineStr">
         <is>
           <t>These groups are taken as a whole even if only a part is producing meat, milk or eggs. Taken as the last historical value</t>
@@ -2645,16 +2518,14 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Ovines dairy productivity</t>
+          <t>Porcines productivity</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>kg/LU</t>
-        </is>
-      </c>
-      <c r="C52" t="inlineStr"/>
-      <c r="D52" t="inlineStr"/>
+          <t>kgcarcass/LU</t>
+        </is>
+      </c>
       <c r="E52" t="inlineStr">
         <is>
           <t>These groups are taken as a whole even if only a part is producing meat, milk or eggs. Taken as the last historical value</t>
@@ -2664,16 +2535,14 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Caprines dairy productivity</t>
+          <t>Poultry productivity</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>kg/LU</t>
-        </is>
-      </c>
-      <c r="C53" t="inlineStr"/>
-      <c r="D53" t="inlineStr"/>
+          <t>kgcarcass/LU</t>
+        </is>
+      </c>
       <c r="E53" t="inlineStr">
         <is>
           <t>These groups are taken as a whole even if only a part is producing meat, milk or eggs. Taken as the last historical value</t>
@@ -2683,19 +2552,168 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
+          <t>Bovines dairy productivity</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>kg/LU</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>These groups are taken as a whole even if only a part is producing meat, milk or eggs. Taken as the last historical value</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Ovines dairy productivity</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>kg/LU</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>These groups are taken as a whole even if only a part is producing meat, milk or eggs. Taken as the last historical value</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>Caprines dairy productivity</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>kg/LU</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>These groups are taken as a whole even if only a part is producing meat, milk or eggs. Taken as the last historical value</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
           <t>Poultry dairy productivity</t>
         </is>
       </c>
-      <c r="B54" t="inlineStr">
+      <c r="B57" t="inlineStr">
         <is>
           <t>kg/LU</t>
         </is>
       </c>
-      <c r="C54" t="inlineStr"/>
-      <c r="D54" t="inlineStr"/>
-      <c r="E54" t="inlineStr">
+      <c r="E57" t="inlineStr">
         <is>
           <t>These groups are taken as a whole even if only a part is producing meat, milk or eggs. Taken as the last historical value</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>Share of crop residues in methaniser</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>prop</t>
+        </is>
+      </c>
+      <c r="C58" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>Adapted from ONRB data</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>Share of green waste in methaniser</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>prop</t>
+        </is>
+      </c>
+      <c r="C59" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>Adapted from ONRB data</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>Share of dedicated culture in methaniser</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>prop</t>
+        </is>
+      </c>
+      <c r="C60" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>Adapted from ONRB data</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>Share of animal food industry in methaniser</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>prop</t>
+        </is>
+      </c>
+      <c r="C61" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>Adapted from ONRB data</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>Share of livestock effluent in methaniser</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>prop</t>
+        </is>
+      </c>
+      <c r="C62" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>Adapted from ONRB data</t>
         </is>
       </c>
     </row>

--- a/src/grafs_e/data/scenario_region/Linear/Loire aval.xlsx
+++ b/src/grafs_e/data/scenario_region/Linear/Loire aval.xlsx
@@ -550,7 +550,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E14"/>
+  <dimension ref="A1:E13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -600,24 +600,24 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Urban population</t>
+          <t>Total per capita protein ingestion</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>%</t>
+          <t>kgN/cap/yr</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Logistic</t>
+          <t>Taken as the last historical value</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Total per capita protein ingestion</t>
+          <t>Vegetal per capita protein ingestion</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -634,7 +634,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Vegetal per capita protein ingestion</t>
+          <t>Edible animal per capita protein ingestion (excl fish)</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -651,24 +651,24 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Edible animal per capita protein ingestion (excl fish)</t>
+          <t>Arable area</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>kgN/cap/yr</t>
+          <t>ha</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Taken as the last historical value</t>
+          <t>Historical trend</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Arable area</t>
+          <t>Permanent grassland area</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -685,24 +685,24 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Permanent grassland area</t>
+          <t>Import of vegetal pdcts</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>ha</t>
+          <t>ktN</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Historical trend</t>
+          <t>2006 data. Used as a goal but may be adjusted according to territory situation</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Import of vegetal pdcts</t>
+          <t>Export of vegetal pdcts</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -719,41 +719,41 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Export of vegetal pdcts</t>
+          <t>Total LU</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>ktN</t>
+          <t>LU</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2006 data. Used as a goal but may be adjusted according to territory situation</t>
+          <t>Historical trend, see prop for each livestock in technical sheet</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Total LU</t>
+          <t>Synth N fertilizer application to cropland</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>LU</t>
+          <t>kgN/ha/yr</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Historical trend, see prop for each livestock in technical sheet</t>
+          <t>No business as usual: computed with optimization model to fertilize all crops</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Synth N fertilizer application to cropland</t>
+          <t>Synth N fertilizer application to grassland</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -770,32 +770,15 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Synth N fertilizer application to grassland</t>
+          <t>Methaniser production</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>kgN/ha/yr</t>
+          <t>GWh/yr</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
-        <is>
-          <t>No business as usual: computed with optimization model to fertilize all crops</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>Methaniser production</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>GWh/yr</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
         <is>
           <t>Regional 2021 data mapped on 2006 33 region plant production. Used as a goal but may be adjusted according to territory situation</t>
         </is>
@@ -1647,7 +1630,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E62"/>
+  <dimension ref="A1:F63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1676,6 +1659,11 @@
           <t>Comment</t>
         </is>
       </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -1691,6 +1679,9 @@
           <t>Weight for the optimization model</t>
         </is>
       </c>
+      <c r="F2" t="n">
+        <v/>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -1706,6 +1697,9 @@
           <t>Weight for the optimization model</t>
         </is>
       </c>
+      <c r="F3" t="n">
+        <v/>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1721,6 +1715,9 @@
           <t>Weight for the optimization model</t>
         </is>
       </c>
+      <c r="F4" t="n">
+        <v/>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1736,6 +1733,9 @@
           <t>Weight for the optimization model</t>
         </is>
       </c>
+      <c r="F5" t="n">
+        <v/>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1751,6 +1751,9 @@
           <t>Weight for the optimization model</t>
         </is>
       </c>
+      <c r="F6" t="n">
+        <v/>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1766,28 +1769,31 @@
           <t>Weight for the optimization model</t>
         </is>
       </c>
+      <c r="F7" t="n">
+        <v/>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>N recycling rate of human excretion in urban area</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
+          <t>Urban population</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Logistic</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
         <is>
           <t>%</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>Taken as the last historical value</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>N recycling rate of human excretion in rural area</t>
+          <t>N recycling rate of human excretion in urban area</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1799,12 +1805,15 @@
         <is>
           <t>Taken as the last historical value</t>
         </is>
+      </c>
+      <c r="F9" t="n">
+        <v/>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>NH3 volatilization coefficient for synthetic nitrogen</t>
+          <t>N recycling rate of human excretion in rural area</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1816,12 +1825,15 @@
         <is>
           <t>Taken as the last historical value</t>
         </is>
+      </c>
+      <c r="F10" t="n">
+        <v/>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Indirect N2O volatilization coefficient for synthetic nitrogen</t>
+          <t>NH3 volatilization coefficient for synthetic nitrogen</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1833,29 +1845,35 @@
         <is>
           <t>Taken as the last historical value</t>
         </is>
+      </c>
+      <c r="F11" t="n">
+        <v/>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>kgN excreted by bovines LU</t>
+          <t>Indirect N2O volatilization coefficient for synthetic nitrogen</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>kgN</t>
+          <t>%</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Historical trend</t>
-        </is>
+          <t>Taken as the last historical value</t>
+        </is>
+      </c>
+      <c r="F12" t="n">
+        <v/>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>kgN excreted by equines LU</t>
+          <t>kgN excreted by bovines LU</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1867,12 +1885,15 @@
         <is>
           <t>Historical trend</t>
         </is>
+      </c>
+      <c r="F13" t="n">
+        <v/>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>kgN excreted by caprines LU</t>
+          <t>kgN excreted by equines LU</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1884,12 +1905,15 @@
         <is>
           <t>Historical trend</t>
         </is>
+      </c>
+      <c r="F14" t="n">
+        <v/>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>kgN excreted by ovines LU</t>
+          <t>kgN excreted by caprines LU</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1901,12 +1925,15 @@
         <is>
           <t>Historical trend</t>
         </is>
+      </c>
+      <c r="F15" t="n">
+        <v/>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>kgN excreted by porcines LU</t>
+          <t>kgN excreted by ovines LU</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1918,12 +1945,15 @@
         <is>
           <t>Historical trend</t>
         </is>
+      </c>
+      <c r="F16" t="n">
+        <v/>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>kgN excreted by poultry LU</t>
+          <t>kgN excreted by porcines LU</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1935,29 +1965,35 @@
         <is>
           <t>Historical trend</t>
         </is>
+      </c>
+      <c r="F17" t="n">
+        <v/>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Bovines % excretion on grassland</t>
+          <t>kgN excreted by poultry LU</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>%</t>
+          <t>kgN</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Taken as the last historical value</t>
-        </is>
+          <t>Historical trend</t>
+        </is>
+      </c>
+      <c r="F18" t="n">
+        <v/>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Bovines % excretion in the barn as litter manure</t>
+          <t>Bovines % excretion on grassland</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1969,12 +2005,15 @@
         <is>
           <t>Taken as the last historical value</t>
         </is>
+      </c>
+      <c r="F19" t="n">
+        <v/>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Bovines % excretion in the barn as other manure</t>
+          <t>Bovines % excretion in the barn as litter manure</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1986,12 +2025,15 @@
         <is>
           <t>Taken as the last historical value</t>
         </is>
+      </c>
+      <c r="F20" t="n">
+        <v/>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Bovines % excretion in the barn as slurry</t>
+          <t>Bovines % excretion in the barn as other manure</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2003,12 +2045,15 @@
         <is>
           <t>Taken as the last historical value</t>
         </is>
+      </c>
+      <c r="F21" t="n">
+        <v/>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Ovines % excretion on grassland</t>
+          <t>Bovines % excretion in the barn as slurry</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2020,12 +2065,15 @@
         <is>
           <t>Taken as the last historical value</t>
         </is>
+      </c>
+      <c r="F22" t="n">
+        <v/>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Ovines % excretion in the barn as litter manure</t>
+          <t>Ovines % excretion on grassland</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2037,12 +2085,15 @@
         <is>
           <t>Taken as the last historical value</t>
         </is>
+      </c>
+      <c r="F23" t="n">
+        <v/>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Ovines % excretion in the barn as other manure</t>
+          <t>Ovines % excretion in the barn as litter manure</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2054,12 +2105,15 @@
         <is>
           <t>Taken as the last historical value</t>
         </is>
+      </c>
+      <c r="F24" t="n">
+        <v/>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Ovines % excretion in the barn as slurry</t>
+          <t>Ovines % excretion in the barn as other manure</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2071,12 +2125,15 @@
         <is>
           <t>Taken as the last historical value</t>
         </is>
+      </c>
+      <c r="F25" t="n">
+        <v/>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Equines % excretion on grassland</t>
+          <t>Ovines % excretion in the barn as slurry</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2088,12 +2145,15 @@
         <is>
           <t>Taken as the last historical value</t>
         </is>
+      </c>
+      <c r="F26" t="n">
+        <v/>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Equines % excretion in the barn as litter manure</t>
+          <t>Equines % excretion on grassland</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2105,12 +2165,15 @@
         <is>
           <t>Taken as the last historical value</t>
         </is>
+      </c>
+      <c r="F27" t="n">
+        <v/>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Equines % excretion in the barn as other manure</t>
+          <t>Equines % excretion in the barn as litter manure</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2122,12 +2185,15 @@
         <is>
           <t>Taken as the last historical value</t>
         </is>
+      </c>
+      <c r="F28" t="n">
+        <v/>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Equines % excretion in the barn as slurry</t>
+          <t>Equines % excretion in the barn as other manure</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2139,12 +2205,15 @@
         <is>
           <t>Taken as the last historical value</t>
         </is>
+      </c>
+      <c r="F29" t="n">
+        <v/>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Caprines % excretion on grassland</t>
+          <t>Equines % excretion in the barn as slurry</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2156,12 +2225,15 @@
         <is>
           <t>Taken as the last historical value</t>
         </is>
+      </c>
+      <c r="F30" t="n">
+        <v/>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Caprines % excretion in the barn as litter manure</t>
+          <t>Caprines % excretion on grassland</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2173,12 +2245,15 @@
         <is>
           <t>Taken as the last historical value</t>
         </is>
+      </c>
+      <c r="F31" t="n">
+        <v/>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Caprines % excretion in the barn as other manure</t>
+          <t>Caprines % excretion in the barn as litter manure</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2190,12 +2265,15 @@
         <is>
           <t>Taken as the last historical value</t>
         </is>
+      </c>
+      <c r="F32" t="n">
+        <v/>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Caprines % excretion in the barn as slurry</t>
+          <t>Caprines % excretion in the barn as other manure</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2207,12 +2285,15 @@
         <is>
           <t>Taken as the last historical value</t>
         </is>
+      </c>
+      <c r="F33" t="n">
+        <v/>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Porcines % excretion on grassland</t>
+          <t>Caprines % excretion in the barn as slurry</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2224,12 +2305,15 @@
         <is>
           <t>Taken as the last historical value</t>
         </is>
+      </c>
+      <c r="F34" t="n">
+        <v/>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Porcines % excretion in the barn as litter manure</t>
+          <t>Porcines % excretion on grassland</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2241,12 +2325,15 @@
         <is>
           <t>Taken as the last historical value</t>
         </is>
+      </c>
+      <c r="F35" t="n">
+        <v/>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Porcines % excretion in the barn as other manure</t>
+          <t>Porcines % excretion in the barn as litter manure</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2258,12 +2345,15 @@
         <is>
           <t>Taken as the last historical value</t>
         </is>
+      </c>
+      <c r="F36" t="n">
+        <v/>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Porcines % excretion in the barn as slurry</t>
+          <t>Porcines % excretion in the barn as other manure</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2275,12 +2365,15 @@
         <is>
           <t>Taken as the last historical value</t>
         </is>
+      </c>
+      <c r="F37" t="n">
+        <v/>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Poultry % excretion on grassland</t>
+          <t>Porcines % excretion in the barn as slurry</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2292,12 +2385,15 @@
         <is>
           <t>Taken as the last historical value</t>
         </is>
+      </c>
+      <c r="F38" t="n">
+        <v/>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Poultry % excretion in the barn as litter manure</t>
+          <t>Poultry % excretion on grassland</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2309,12 +2405,15 @@
         <is>
           <t>Taken as the last historical value</t>
         </is>
+      </c>
+      <c r="F39" t="n">
+        <v/>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Poultry % excretion in the barn as other manure</t>
+          <t>Poultry % excretion in the barn as litter manure</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2326,12 +2425,15 @@
         <is>
           <t>Taken as the last historical value</t>
         </is>
+      </c>
+      <c r="F40" t="n">
+        <v/>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Poultry % excretion in the barn as slurry</t>
+          <t>Poultry % excretion in the barn as other manure</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -2343,29 +2445,35 @@
         <is>
           <t>Taken as the last historical value</t>
         </is>
+      </c>
+      <c r="F41" t="n">
+        <v/>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Bovines LU</t>
+          <t>Poultry % excretion in the barn as slurry</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>prop</t>
+          <t>%</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
           <t>Taken as the last historical value</t>
         </is>
+      </c>
+      <c r="F42" t="n">
+        <v/>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Ovines LU</t>
+          <t>Bovines LU</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -2377,12 +2485,15 @@
         <is>
           <t>Taken as the last historical value</t>
         </is>
+      </c>
+      <c r="F43" t="n">
+        <v/>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Caprines LU</t>
+          <t>Ovines LU</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -2394,12 +2505,15 @@
         <is>
           <t>Taken as the last historical value</t>
         </is>
+      </c>
+      <c r="F44" t="n">
+        <v/>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Equines LU</t>
+          <t>Caprines LU</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -2411,12 +2525,15 @@
         <is>
           <t>Taken as the last historical value</t>
         </is>
+      </c>
+      <c r="F45" t="n">
+        <v/>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Porcines LU</t>
+          <t>Equines LU</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -2428,12 +2545,15 @@
         <is>
           <t>Taken as the last historical value</t>
         </is>
+      </c>
+      <c r="F46" t="n">
+        <v/>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Poultry LU</t>
+          <t>Porcines LU</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -2445,29 +2565,35 @@
         <is>
           <t>Taken as the last historical value</t>
         </is>
+      </c>
+      <c r="F47" t="n">
+        <v/>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Bovines productivity</t>
+          <t>Poultry LU</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>kgcarcass/LU</t>
+          <t>prop</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>These groups are taken as a whole even if only a part is producing meat, milk or eggs. Taken as the last historical value</t>
-        </is>
+          <t>Taken as the last historical value</t>
+        </is>
+      </c>
+      <c r="F48" t="n">
+        <v/>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Ovines productivity</t>
+          <t>Bovines productivity</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2479,12 +2605,15 @@
         <is>
           <t>These groups are taken as a whole even if only a part is producing meat, milk or eggs. Taken as the last historical value</t>
         </is>
+      </c>
+      <c r="F49" t="n">
+        <v/>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Caprines productivity</t>
+          <t>Ovines productivity</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -2496,12 +2625,15 @@
         <is>
           <t>These groups are taken as a whole even if only a part is producing meat, milk or eggs. Taken as the last historical value</t>
         </is>
+      </c>
+      <c r="F50" t="n">
+        <v/>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Equines productivity</t>
+          <t>Caprines productivity</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -2513,12 +2645,15 @@
         <is>
           <t>These groups are taken as a whole even if only a part is producing meat, milk or eggs. Taken as the last historical value</t>
         </is>
+      </c>
+      <c r="F51" t="n">
+        <v/>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Porcines productivity</t>
+          <t>Equines productivity</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -2530,12 +2665,15 @@
         <is>
           <t>These groups are taken as a whole even if only a part is producing meat, milk or eggs. Taken as the last historical value</t>
         </is>
+      </c>
+      <c r="F52" t="n">
+        <v/>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Poultry productivity</t>
+          <t>Porcines productivity</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -2547,29 +2685,35 @@
         <is>
           <t>These groups are taken as a whole even if only a part is producing meat, milk or eggs. Taken as the last historical value</t>
         </is>
+      </c>
+      <c r="F53" t="n">
+        <v/>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Bovines dairy productivity</t>
+          <t>Poultry productivity</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>kg/LU</t>
+          <t>kgcarcass/LU</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
           <t>These groups are taken as a whole even if only a part is producing meat, milk or eggs. Taken as the last historical value</t>
         </is>
+      </c>
+      <c r="F54" t="n">
+        <v/>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Ovines dairy productivity</t>
+          <t>Bovines dairy productivity</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -2581,12 +2725,15 @@
         <is>
           <t>These groups are taken as a whole even if only a part is producing meat, milk or eggs. Taken as the last historical value</t>
         </is>
+      </c>
+      <c r="F55" t="n">
+        <v/>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Caprines dairy productivity</t>
+          <t>Ovines dairy productivity</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -2598,12 +2745,15 @@
         <is>
           <t>These groups are taken as a whole even if only a part is producing meat, milk or eggs. Taken as the last historical value</t>
         </is>
+      </c>
+      <c r="F56" t="n">
+        <v/>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Poultry dairy productivity</t>
+          <t>Caprines dairy productivity</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -2615,32 +2765,35 @@
         <is>
           <t>These groups are taken as a whole even if only a part is producing meat, milk or eggs. Taken as the last historical value</t>
         </is>
+      </c>
+      <c r="F57" t="n">
+        <v/>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Share of crop residues in methaniser</t>
+          <t>Poultry dairy productivity</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>prop</t>
-        </is>
-      </c>
-      <c r="C58" t="n">
-        <v>0.06</v>
+          <t>kg/LU</t>
+        </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Adapted from ONRB data</t>
-        </is>
+          <t>These groups are taken as a whole even if only a part is producing meat, milk or eggs. Taken as the last historical value</t>
+        </is>
+      </c>
+      <c r="F58" t="n">
+        <v/>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Share of green waste in methaniser</t>
+          <t>Share of crop residues in methaniser</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -2649,18 +2802,21 @@
         </is>
       </c>
       <c r="C59" t="n">
-        <v>0.02</v>
+        <v>0.06</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
           <t>Adapted from ONRB data</t>
         </is>
+      </c>
+      <c r="F59" t="n">
+        <v/>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Share of dedicated culture in methaniser</t>
+          <t>Share of green waste in methaniser</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -2669,18 +2825,21 @@
         </is>
       </c>
       <c r="C60" t="n">
-        <v>0.09</v>
+        <v>0.02</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
           <t>Adapted from ONRB data</t>
         </is>
+      </c>
+      <c r="F60" t="n">
+        <v/>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Share of animal food industry in methaniser</t>
+          <t>Share of dedicated culture in methaniser</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -2689,32 +2848,61 @@
         </is>
       </c>
       <c r="C61" t="n">
-        <v>0.04</v>
+        <v>0.09</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
           <t>Adapted from ONRB data</t>
         </is>
+      </c>
+      <c r="F61" t="n">
+        <v/>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
+          <t>Share of animal food industry in methaniser</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>prop</t>
+        </is>
+      </c>
+      <c r="C62" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>Adapted from ONRB data</t>
+        </is>
+      </c>
+      <c r="F62" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
           <t>Share of livestock effluent in methaniser</t>
         </is>
       </c>
-      <c r="B62" t="inlineStr">
+      <c r="B63" t="inlineStr">
         <is>
           <t>prop</t>
         </is>
       </c>
-      <c r="C62" t="n">
+      <c r="C63" t="n">
         <v>0.79</v>
       </c>
-      <c r="E62" t="inlineStr">
+      <c r="E63" t="inlineStr">
         <is>
           <t>Adapted from ONRB data</t>
         </is>
+      </c>
+      <c r="F63" t="n">
+        <v/>
       </c>
     </row>
   </sheetData>

--- a/src/grafs_e/data/scenario_region/Linear/Loire aval.xlsx
+++ b/src/grafs_e/data/scenario_region/Linear/Loire aval.xlsx
@@ -795,38 +795,43 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F37"/>
+  <dimension ref="A1:G36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Crops</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>Area proportion (%)</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>Enforce Area</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>a</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>b</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>r2</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>Straw to Grain Ratio</t>
         </is>
       </c>
     </row>
@@ -851,6 +856,9 @@
       <c r="F2" t="n">
         <v>0.98</v>
       </c>
+      <c r="G2" t="n">
+        <v>0.118</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -873,6 +881,9 @@
       <c r="F3" t="n">
         <v>0.96</v>
       </c>
+      <c r="G3" t="n">
+        <v>0.131</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -895,6 +906,9 @@
       <c r="F4" t="n">
         <v>0.96</v>
       </c>
+      <c r="G4" t="n">
+        <v>0.121</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -917,11 +931,14 @@
       <c r="F5" t="n">
         <v>1</v>
       </c>
+      <c r="G5" t="n">
+        <v>0.094</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Grain maize</t>
+          <t>Maize</t>
         </is>
       </c>
       <c r="B6" t="n">
@@ -939,6 +956,9 @@
       <c r="F6" t="n">
         <v>0.83</v>
       </c>
+      <c r="G6" t="n">
+        <v>0.124</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -961,6 +981,9 @@
       <c r="F7" t="n">
         <v>0</v>
       </c>
+      <c r="G7" t="n">
+        <v/>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -983,231 +1006,264 @@
       <c r="F8" t="n">
         <v>0.98</v>
       </c>
+      <c r="G8" t="n">
+        <v>0.126</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Straw</t>
+          <t>Rapeseed</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0</v>
+        <v>4.713783796503458</v>
       </c>
       <c r="C9" t="b">
         <v>0</v>
       </c>
       <c r="D9" t="n">
-        <v>0.98</v>
+        <v>0.73</v>
       </c>
       <c r="E9" t="n">
-        <v>110.14</v>
+        <v>189.27</v>
       </c>
       <c r="F9" t="n">
-        <v>0.7</v>
+        <v>0.73</v>
+      </c>
+      <c r="G9" t="n">
+        <v/>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Rapeseed</t>
+          <t>Sunflower</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>4.713783796503458</v>
+        <v>2.86744605760277</v>
       </c>
       <c r="C10" t="b">
         <v>0</v>
       </c>
       <c r="D10" t="n">
-        <v>0.73</v>
+        <v>0.61</v>
       </c>
       <c r="E10" t="n">
-        <v>189.27</v>
+        <v>104.18</v>
       </c>
       <c r="F10" t="n">
-        <v>0.73</v>
+        <v>0.64</v>
+      </c>
+      <c r="G10" t="n">
+        <v/>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Sunflower</t>
+          <t>Soybean</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>2.86744605760277</v>
+        <v>0.03193809690416213</v>
       </c>
       <c r="C11" t="b">
         <v>0</v>
       </c>
       <c r="D11" t="n">
-        <v>0.61</v>
+        <v>0.77</v>
       </c>
       <c r="E11" t="n">
-        <v>104.18</v>
+        <v>174.25</v>
       </c>
       <c r="F11" t="n">
-        <v>0.64</v>
+        <v>1</v>
+      </c>
+      <c r="G11" t="n">
+        <v/>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Soybean</t>
+          <t>Other oil crops</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.03193809690416213</v>
+        <v>0.1160943750584753</v>
       </c>
       <c r="C12" t="b">
         <v>0</v>
       </c>
       <c r="D12" t="n">
-        <v>0.77</v>
+        <v>0.9</v>
       </c>
       <c r="E12" t="n">
-        <v>174.25</v>
+        <v>98.65000000000001</v>
       </c>
       <c r="F12" t="n">
-        <v>1</v>
+        <v>0.59</v>
+      </c>
+      <c r="G12" t="n">
+        <v/>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Other oil crops</t>
+          <t>Horse beans and faba beans</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.1160943750584753</v>
+        <v>0.2300635915777003</v>
       </c>
       <c r="C13" t="b">
         <v>0</v>
       </c>
       <c r="D13" t="n">
-        <v>0.9</v>
+        <v>0.76</v>
       </c>
       <c r="E13" t="n">
-        <v>98.65000000000001</v>
+        <v>148.16</v>
       </c>
       <c r="F13" t="n">
-        <v>0.59</v>
+        <v>1</v>
+      </c>
+      <c r="G13" t="n">
+        <v/>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Horse beans and faba beans</t>
+          <t>Peas</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.2300635915777003</v>
+        <v>0.6610457433376676</v>
       </c>
       <c r="C14" t="b">
         <v>0</v>
       </c>
       <c r="D14" t="n">
-        <v>0.76</v>
+        <v>0.74</v>
       </c>
       <c r="E14" t="n">
-        <v>148.16</v>
+        <v>167.09</v>
       </c>
       <c r="F14" t="n">
         <v>1</v>
       </c>
+      <c r="G14" t="n">
+        <v/>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Peas</t>
+          <t>Other protein crops</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.6610457433376676</v>
+        <v>0.09775729280551529</v>
       </c>
       <c r="C15" t="b">
         <v>0</v>
       </c>
       <c r="D15" t="n">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="E15" t="n">
-        <v>167.09</v>
+        <v>116.95</v>
       </c>
       <c r="F15" t="n">
         <v>1</v>
       </c>
+      <c r="G15" t="n">
+        <v/>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Other protein crops</t>
+          <t>Sugar beet</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.09775729280551529</v>
+        <v>0.04620701852484294</v>
       </c>
       <c r="C16" t="b">
         <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>0.75</v>
+        <v>0.79</v>
       </c>
       <c r="E16" t="n">
-        <v>116.95</v>
+        <v>182.4</v>
       </c>
       <c r="F16" t="n">
-        <v>1</v>
+        <v>0.76</v>
+      </c>
+      <c r="G16" t="n">
+        <v/>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Sugar beet</t>
+          <t>Potatoes</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.04620701852484294</v>
+        <v>0.03454900596666969</v>
       </c>
       <c r="C17" t="b">
         <v>0</v>
       </c>
       <c r="D17" t="n">
+        <v>0.64</v>
+      </c>
+      <c r="E17" t="n">
+        <v>67.51000000000001</v>
+      </c>
+      <c r="F17" t="n">
         <v>0.79</v>
       </c>
-      <c r="E17" t="n">
-        <v>182.4</v>
-      </c>
-      <c r="F17" t="n">
-        <v>0.76</v>
+      <c r="G17" t="n">
+        <v/>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Potatoes</t>
+          <t>Other roots</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.03454900596666969</v>
+        <v>0</v>
       </c>
       <c r="C18" t="b">
         <v>0</v>
       </c>
       <c r="D18" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="E18" t="n">
+        <v>117.05</v>
+      </c>
+      <c r="F18" t="n">
         <v>0.64</v>
       </c>
-      <c r="E18" t="n">
-        <v>67.51000000000001</v>
-      </c>
-      <c r="F18" t="n">
-        <v>0.79</v>
+      <c r="G18" t="n">
+        <v/>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Other roots</t>
+          <t>Green peas</t>
         </is>
       </c>
       <c r="B19" t="n">
@@ -1217,19 +1273,22 @@
         <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>0.65</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="E19" t="n">
-        <v>117.05</v>
+        <v>37.05</v>
       </c>
       <c r="F19" t="n">
-        <v>0.64</v>
+        <v>0.93</v>
+      </c>
+      <c r="G19" t="n">
+        <v/>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Green peas</t>
+          <t>Dry beans</t>
         </is>
       </c>
       <c r="B20" t="n">
@@ -1239,19 +1298,22 @@
         <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.74</v>
       </c>
       <c r="E20" t="n">
-        <v>37.05</v>
+        <v>83.7</v>
       </c>
       <c r="F20" t="n">
-        <v>0.93</v>
+        <v>0.99</v>
+      </c>
+      <c r="G20" t="n">
+        <v/>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Dry beans</t>
+          <t>Green beans</t>
         </is>
       </c>
       <c r="B21" t="n">
@@ -1261,19 +1323,22 @@
         <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>0.74</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="E21" t="n">
-        <v>83.7</v>
+        <v>49.51</v>
       </c>
       <c r="F21" t="n">
-        <v>0.99</v>
+        <v>0.98</v>
+      </c>
+      <c r="G21" t="n">
+        <v/>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Green beans</t>
+          <t>Dry vegetables</t>
         </is>
       </c>
       <c r="B22" t="n">
@@ -1283,19 +1348,22 @@
         <v>0</v>
       </c>
       <c r="D22" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.98</v>
       </c>
       <c r="E22" t="n">
-        <v>49.51</v>
+        <v>83.62</v>
       </c>
       <c r="F22" t="n">
-        <v>0.98</v>
+        <v>1</v>
+      </c>
+      <c r="G22" t="n">
+        <v/>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Dry vegetables</t>
+          <t>Dry fruits</t>
         </is>
       </c>
       <c r="B23" t="n">
@@ -1305,19 +1373,22 @@
         <v>0</v>
       </c>
       <c r="D23" t="n">
-        <v>0.98</v>
+        <v>0.75</v>
       </c>
       <c r="E23" t="n">
-        <v>83.62</v>
+        <v>34.15</v>
       </c>
       <c r="F23" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="G23" t="n">
+        <v/>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Dry fruits</t>
+          <t>Squash and melons</t>
         </is>
       </c>
       <c r="B24" t="n">
@@ -1327,19 +1398,22 @@
         <v>0</v>
       </c>
       <c r="D24" t="n">
-        <v>0.75</v>
+        <v>0.99</v>
       </c>
       <c r="E24" t="n">
-        <v>34.15</v>
+        <v>48.34</v>
       </c>
       <c r="F24" t="n">
-        <v>0</v>
+        <v>0.86</v>
+      </c>
+      <c r="G24" t="n">
+        <v/>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Squash and melons</t>
+          <t>Cabbage</t>
         </is>
       </c>
       <c r="B25" t="n">
@@ -1349,19 +1423,22 @@
         <v>0</v>
       </c>
       <c r="D25" t="n">
-        <v>0.99</v>
+        <v>0.33</v>
       </c>
       <c r="E25" t="n">
-        <v>48.34</v>
+        <v>71.7</v>
       </c>
       <c r="F25" t="n">
-        <v>0.86</v>
+        <v>-0.06</v>
+      </c>
+      <c r="G25" t="n">
+        <v/>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Cabbage</t>
+          <t>Leaves vegetables</t>
         </is>
       </c>
       <c r="B26" t="n">
@@ -1371,19 +1448,22 @@
         <v>0</v>
       </c>
       <c r="D26" t="n">
-        <v>0.33</v>
+        <v>0.98</v>
       </c>
       <c r="E26" t="n">
-        <v>71.7</v>
+        <v>35.47</v>
       </c>
       <c r="F26" t="n">
-        <v>-0.06</v>
+        <v>0</v>
+      </c>
+      <c r="G26" t="n">
+        <v/>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Leaves vegetables</t>
+          <t>Fruits</t>
         </is>
       </c>
       <c r="B27" t="n">
@@ -1393,19 +1473,22 @@
         <v>0</v>
       </c>
       <c r="D27" t="n">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="E27" t="n">
-        <v>35.47</v>
+        <v>38.5</v>
       </c>
       <c r="F27" t="n">
-        <v>0</v>
+        <v>0.99</v>
+      </c>
+      <c r="G27" t="n">
+        <v/>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Fruits</t>
+          <t>Olives</t>
         </is>
       </c>
       <c r="B28" t="n">
@@ -1415,19 +1498,22 @@
         <v>0</v>
       </c>
       <c r="D28" t="n">
-        <v>0.99</v>
+        <v>0</v>
       </c>
       <c r="E28" t="n">
-        <v>38.5</v>
+        <v>0</v>
       </c>
       <c r="F28" t="n">
-        <v>0.99</v>
+        <v>0</v>
+      </c>
+      <c r="G28" t="n">
+        <v/>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Olives</t>
+          <t>Citrus</t>
         </is>
       </c>
       <c r="B29" t="n">
@@ -1444,12 +1530,15 @@
       </c>
       <c r="F29" t="n">
         <v>0</v>
+      </c>
+      <c r="G29" t="n">
+        <v/>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Citrus</t>
+          <t>Hemp</t>
         </is>
       </c>
       <c r="B30" t="n">
@@ -1459,19 +1548,22 @@
         <v>0</v>
       </c>
       <c r="D30" t="n">
-        <v>0</v>
+        <v>0.82</v>
       </c>
       <c r="E30" t="n">
-        <v>0</v>
+        <v>18.98</v>
       </c>
       <c r="F30" t="n">
-        <v>0</v>
+        <v>0.43</v>
+      </c>
+      <c r="G30" t="n">
+        <v/>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Hemp</t>
+          <t>Flax</t>
         </is>
       </c>
       <c r="B31" t="n">
@@ -1481,142 +1573,138 @@
         <v>0</v>
       </c>
       <c r="D31" t="n">
-        <v>0.82</v>
+        <v>1</v>
       </c>
       <c r="E31" t="n">
-        <v>18.98</v>
+        <v>15.85</v>
       </c>
       <c r="F31" t="n">
-        <v>0.43</v>
+        <v>0.8</v>
+      </c>
+      <c r="G31" t="n">
+        <v/>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Flax</t>
+          <t>Forage maize</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>0</v>
+        <v>17.08457452874127</v>
       </c>
       <c r="C32" t="b">
         <v>0</v>
       </c>
       <c r="D32" t="n">
-        <v>1</v>
+        <v>0.95</v>
       </c>
       <c r="E32" t="n">
-        <v>15.85</v>
+        <v>340.93</v>
       </c>
       <c r="F32" t="n">
-        <v>0.8</v>
+        <v>0.98</v>
+      </c>
+      <c r="G32" t="n">
+        <v/>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Forage maize</t>
+          <t>Forage cabbages</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>17.08457452874127</v>
+        <v>0.01153360353349177</v>
       </c>
       <c r="C33" t="b">
         <v>0</v>
       </c>
       <c r="D33" t="n">
-        <v>0.95</v>
+        <v>0.93</v>
       </c>
       <c r="E33" t="n">
-        <v>340.93</v>
+        <v>139.93</v>
       </c>
       <c r="F33" t="n">
-        <v>0.98</v>
+        <v>0.8</v>
+      </c>
+      <c r="G33" t="n">
+        <v/>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Forage cabbages</t>
+          <t>Alfalfa and clover</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>0.01153360353349177</v>
+        <v>0.711806673018047</v>
       </c>
       <c r="C34" t="b">
         <v>0</v>
       </c>
       <c r="D34" t="n">
-        <v>0.93</v>
+        <v>0.59</v>
       </c>
       <c r="E34" t="n">
-        <v>139.93</v>
+        <v>188.66</v>
       </c>
       <c r="F34" t="n">
-        <v>0.8</v>
+        <v>0.97</v>
+      </c>
+      <c r="G34" t="n">
+        <v/>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Alfalfa and clover</t>
+          <t>Non-legume temporary meadow</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>0.711806673018047</v>
+        <v>29.17065473553495</v>
       </c>
       <c r="C35" t="b">
         <v>0</v>
       </c>
       <c r="D35" t="n">
-        <v>0.59</v>
+        <v>0.8</v>
       </c>
       <c r="E35" t="n">
-        <v>188.66</v>
+        <v>346.67</v>
       </c>
       <c r="F35" t="n">
-        <v>0.97</v>
+        <v>0.8</v>
+      </c>
+      <c r="G35" t="n">
+        <v/>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Non-legume temporary meadow</t>
-        </is>
-      </c>
-      <c r="B36" t="n">
-        <v>29.17065473553495</v>
+          <t xml:space="preserve">Natural meadow </t>
+        </is>
       </c>
       <c r="C36" t="b">
         <v>0</v>
       </c>
       <c r="D36" t="n">
-        <v>0.8</v>
+        <v>0.77</v>
       </c>
       <c r="E36" t="n">
-        <v>346.67</v>
+        <v>115.27</v>
       </c>
       <c r="F36" t="n">
-        <v>0.8</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Natural meadow </t>
-        </is>
-      </c>
-      <c r="C37" t="b">
-        <v>0</v>
-      </c>
-      <c r="D37" t="n">
-        <v>0.77</v>
-      </c>
-      <c r="E37" t="n">
-        <v>115.27</v>
-      </c>
-      <c r="F37" t="n">
         <v>0.44</v>
+      </c>
+      <c r="G36" t="n">
+        <v/>
       </c>
     </row>
   </sheetData>
@@ -1679,9 +1767,6 @@
           <t>Weight for the optimization model</t>
         </is>
       </c>
-      <c r="F2" t="n">
-        <v/>
-      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -1697,9 +1782,6 @@
           <t>Weight for the optimization model</t>
         </is>
       </c>
-      <c r="F3" t="n">
-        <v/>
-      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1715,9 +1797,6 @@
           <t>Weight for the optimization model</t>
         </is>
       </c>
-      <c r="F4" t="n">
-        <v/>
-      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1733,9 +1812,6 @@
           <t>Weight for the optimization model</t>
         </is>
       </c>
-      <c r="F5" t="n">
-        <v/>
-      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1751,9 +1827,6 @@
           <t>Weight for the optimization model</t>
         </is>
       </c>
-      <c r="F6" t="n">
-        <v/>
-      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1769,9 +1842,6 @@
           <t>Weight for the optimization model</t>
         </is>
       </c>
-      <c r="F7" t="n">
-        <v/>
-      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1806,9 +1876,6 @@
           <t>Taken as the last historical value</t>
         </is>
       </c>
-      <c r="F9" t="n">
-        <v/>
-      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1826,9 +1893,6 @@
           <t>Taken as the last historical value</t>
         </is>
       </c>
-      <c r="F10" t="n">
-        <v/>
-      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1846,9 +1910,6 @@
           <t>Taken as the last historical value</t>
         </is>
       </c>
-      <c r="F11" t="n">
-        <v/>
-      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1866,9 +1927,6 @@
           <t>Taken as the last historical value</t>
         </is>
       </c>
-      <c r="F12" t="n">
-        <v/>
-      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1886,9 +1944,6 @@
           <t>Historical trend</t>
         </is>
       </c>
-      <c r="F13" t="n">
-        <v/>
-      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1906,9 +1961,6 @@
           <t>Historical trend</t>
         </is>
       </c>
-      <c r="F14" t="n">
-        <v/>
-      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1926,9 +1978,6 @@
           <t>Historical trend</t>
         </is>
       </c>
-      <c r="F15" t="n">
-        <v/>
-      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1946,9 +1995,6 @@
           <t>Historical trend</t>
         </is>
       </c>
-      <c r="F16" t="n">
-        <v/>
-      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1966,9 +2012,6 @@
           <t>Historical trend</t>
         </is>
       </c>
-      <c r="F17" t="n">
-        <v/>
-      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1986,9 +2029,6 @@
           <t>Historical trend</t>
         </is>
       </c>
-      <c r="F18" t="n">
-        <v/>
-      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -2006,9 +2046,6 @@
           <t>Taken as the last historical value</t>
         </is>
       </c>
-      <c r="F19" t="n">
-        <v/>
-      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -2026,9 +2063,6 @@
           <t>Taken as the last historical value</t>
         </is>
       </c>
-      <c r="F20" t="n">
-        <v/>
-      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -2046,9 +2080,6 @@
           <t>Taken as the last historical value</t>
         </is>
       </c>
-      <c r="F21" t="n">
-        <v/>
-      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -2066,9 +2097,6 @@
           <t>Taken as the last historical value</t>
         </is>
       </c>
-      <c r="F22" t="n">
-        <v/>
-      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -2086,9 +2114,6 @@
           <t>Taken as the last historical value</t>
         </is>
       </c>
-      <c r="F23" t="n">
-        <v/>
-      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -2106,9 +2131,6 @@
           <t>Taken as the last historical value</t>
         </is>
       </c>
-      <c r="F24" t="n">
-        <v/>
-      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -2126,9 +2148,6 @@
           <t>Taken as the last historical value</t>
         </is>
       </c>
-      <c r="F25" t="n">
-        <v/>
-      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -2146,9 +2165,6 @@
           <t>Taken as the last historical value</t>
         </is>
       </c>
-      <c r="F26" t="n">
-        <v/>
-      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -2166,9 +2182,6 @@
           <t>Taken as the last historical value</t>
         </is>
       </c>
-      <c r="F27" t="n">
-        <v/>
-      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -2186,9 +2199,6 @@
           <t>Taken as the last historical value</t>
         </is>
       </c>
-      <c r="F28" t="n">
-        <v/>
-      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -2206,9 +2216,6 @@
           <t>Taken as the last historical value</t>
         </is>
       </c>
-      <c r="F29" t="n">
-        <v/>
-      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -2226,9 +2233,6 @@
           <t>Taken as the last historical value</t>
         </is>
       </c>
-      <c r="F30" t="n">
-        <v/>
-      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -2246,9 +2250,6 @@
           <t>Taken as the last historical value</t>
         </is>
       </c>
-      <c r="F31" t="n">
-        <v/>
-      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -2266,9 +2267,6 @@
           <t>Taken as the last historical value</t>
         </is>
       </c>
-      <c r="F32" t="n">
-        <v/>
-      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -2286,9 +2284,6 @@
           <t>Taken as the last historical value</t>
         </is>
       </c>
-      <c r="F33" t="n">
-        <v/>
-      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -2306,9 +2301,6 @@
           <t>Taken as the last historical value</t>
         </is>
       </c>
-      <c r="F34" t="n">
-        <v/>
-      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -2326,9 +2318,6 @@
           <t>Taken as the last historical value</t>
         </is>
       </c>
-      <c r="F35" t="n">
-        <v/>
-      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -2346,9 +2335,6 @@
           <t>Taken as the last historical value</t>
         </is>
       </c>
-      <c r="F36" t="n">
-        <v/>
-      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -2366,9 +2352,6 @@
           <t>Taken as the last historical value</t>
         </is>
       </c>
-      <c r="F37" t="n">
-        <v/>
-      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -2386,9 +2369,6 @@
           <t>Taken as the last historical value</t>
         </is>
       </c>
-      <c r="F38" t="n">
-        <v/>
-      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -2406,9 +2386,6 @@
           <t>Taken as the last historical value</t>
         </is>
       </c>
-      <c r="F39" t="n">
-        <v/>
-      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -2426,9 +2403,6 @@
           <t>Taken as the last historical value</t>
         </is>
       </c>
-      <c r="F40" t="n">
-        <v/>
-      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -2446,9 +2420,6 @@
           <t>Taken as the last historical value</t>
         </is>
       </c>
-      <c r="F41" t="n">
-        <v/>
-      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -2466,9 +2437,6 @@
           <t>Taken as the last historical value</t>
         </is>
       </c>
-      <c r="F42" t="n">
-        <v/>
-      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -2486,9 +2454,6 @@
           <t>Taken as the last historical value</t>
         </is>
       </c>
-      <c r="F43" t="n">
-        <v/>
-      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -2506,9 +2471,6 @@
           <t>Taken as the last historical value</t>
         </is>
       </c>
-      <c r="F44" t="n">
-        <v/>
-      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -2526,9 +2488,6 @@
           <t>Taken as the last historical value</t>
         </is>
       </c>
-      <c r="F45" t="n">
-        <v/>
-      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -2546,9 +2505,6 @@
           <t>Taken as the last historical value</t>
         </is>
       </c>
-      <c r="F46" t="n">
-        <v/>
-      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -2566,9 +2522,6 @@
           <t>Taken as the last historical value</t>
         </is>
       </c>
-      <c r="F47" t="n">
-        <v/>
-      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -2586,9 +2539,6 @@
           <t>Taken as the last historical value</t>
         </is>
       </c>
-      <c r="F48" t="n">
-        <v/>
-      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -2606,9 +2556,6 @@
           <t>These groups are taken as a whole even if only a part is producing meat, milk or eggs. Taken as the last historical value</t>
         </is>
       </c>
-      <c r="F49" t="n">
-        <v/>
-      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -2626,9 +2573,6 @@
           <t>These groups are taken as a whole even if only a part is producing meat, milk or eggs. Taken as the last historical value</t>
         </is>
       </c>
-      <c r="F50" t="n">
-        <v/>
-      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -2646,9 +2590,6 @@
           <t>These groups are taken as a whole even if only a part is producing meat, milk or eggs. Taken as the last historical value</t>
         </is>
       </c>
-      <c r="F51" t="n">
-        <v/>
-      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -2666,9 +2607,6 @@
           <t>These groups are taken as a whole even if only a part is producing meat, milk or eggs. Taken as the last historical value</t>
         </is>
       </c>
-      <c r="F52" t="n">
-        <v/>
-      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -2686,9 +2624,6 @@
           <t>These groups are taken as a whole even if only a part is producing meat, milk or eggs. Taken as the last historical value</t>
         </is>
       </c>
-      <c r="F53" t="n">
-        <v/>
-      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -2706,9 +2641,6 @@
           <t>These groups are taken as a whole even if only a part is producing meat, milk or eggs. Taken as the last historical value</t>
         </is>
       </c>
-      <c r="F54" t="n">
-        <v/>
-      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -2726,9 +2658,6 @@
           <t>These groups are taken as a whole even if only a part is producing meat, milk or eggs. Taken as the last historical value</t>
         </is>
       </c>
-      <c r="F55" t="n">
-        <v/>
-      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -2746,9 +2675,6 @@
           <t>These groups are taken as a whole even if only a part is producing meat, milk or eggs. Taken as the last historical value</t>
         </is>
       </c>
-      <c r="F56" t="n">
-        <v/>
-      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -2766,9 +2692,6 @@
           <t>These groups are taken as a whole even if only a part is producing meat, milk or eggs. Taken as the last historical value</t>
         </is>
       </c>
-      <c r="F57" t="n">
-        <v/>
-      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -2786,9 +2709,6 @@
           <t>These groups are taken as a whole even if only a part is producing meat, milk or eggs. Taken as the last historical value</t>
         </is>
       </c>
-      <c r="F58" t="n">
-        <v/>
-      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -2809,9 +2729,6 @@
           <t>Adapted from ONRB data</t>
         </is>
       </c>
-      <c r="F59" t="n">
-        <v/>
-      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -2832,9 +2749,6 @@
           <t>Adapted from ONRB data</t>
         </is>
       </c>
-      <c r="F60" t="n">
-        <v/>
-      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -2855,9 +2769,6 @@
           <t>Adapted from ONRB data</t>
         </is>
       </c>
-      <c r="F61" t="n">
-        <v/>
-      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -2878,9 +2789,6 @@
           <t>Adapted from ONRB data</t>
         </is>
       </c>
-      <c r="F62" t="n">
-        <v/>
-      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -2900,9 +2808,6 @@
         <is>
           <t>Adapted from ONRB data</t>
         </is>
-      </c>
-      <c r="F63" t="n">
-        <v/>
       </c>
     </row>
   </sheetData>
